--- a/PresetGroups.xlsx
+++ b/PresetGroups.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2882" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2894" uniqueCount="990">
   <si>
     <t>NAME</t>
   </si>
@@ -113,9 +113,15 @@
     <t>Renew</t>
   </si>
   <si>
+    <t>Communist Party of Austria</t>
+  </si>
+  <si>
     <t>Reformist Movement</t>
   </si>
   <si>
+    <t>KPÖ</t>
+  </si>
+  <si>
     <t>MR</t>
   </si>
   <si>
@@ -125,6 +131,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Mouvement_réformateur_2023.svg/330px-Mouvement_réformateur_2023.svg.png</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Kommunistische_Partei_%C3%96sterreichs_Logo.svg/1920px-Kommunistische_Partei_%C3%96sterreichs_Logo.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>#002BFF</t>
   </si>
   <si>
@@ -149,15 +158,6 @@
     <t>https://i.ibb.co/TxJ3Mzfm/NVA.png</t>
   </si>
   <si>
-    <t>Communist Party of Austria</t>
-  </si>
-  <si>
-    <t>KPÖ</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Kommunistische_Partei_%C3%96sterreichs_Logo.svg/1920px-Kommunistische_Partei_%C3%96sterreichs_Logo.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>#fcbd1b</t>
   </si>
   <si>
@@ -185,21 +185,21 @@
     <t>https://i.ibb.co/1tMy1n5h/cd-v-logo.png</t>
   </si>
   <si>
+    <t>#ff6000</t>
+  </si>
+  <si>
+    <t>Vooruit</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/ym0RdDdw/Vooruit-logo.png</t>
+  </si>
+  <si>
     <t>#AB0000</t>
   </si>
   <si>
     <t>Left</t>
   </si>
   <si>
-    <t>#ff6000</t>
-  </si>
-  <si>
-    <t>Vooruit</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/ym0RdDdw/Vooruit-logo.png</t>
-  </si>
-  <si>
     <t>#FF2900</t>
   </si>
   <si>
@@ -329,6 +329,15 @@
     <t>https://upload.wikimedia.org/wikipedia/en/thumb/f/ff/Logo_of_the_Movement_for_Rights_and_Freedoms.svg/330px-Logo_of_the_Movement_for_Rights_and_Freedoms.svg.png</t>
   </si>
   <si>
+    <t>Progressive Bulgaria</t>
+  </si>
+  <si>
+    <t>PB</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Progressive_Bulgaria.svg/960px-Progressive_Bulgaria.svg.png</t>
+  </si>
+  <si>
     <t>#365CA4</t>
   </si>
   <si>
@@ -353,6 +362,12 @@
     <t>https://i.ibb.co/Vcw3SWFK/image.png</t>
   </si>
   <si>
+    <t>#204A41</t>
+  </si>
+  <si>
+    <t>Non-Inscrits</t>
+  </si>
+  <si>
     <t>#034a80</t>
   </si>
   <si>
@@ -380,15 +395,6 @@
     <t>https://upload.wikimedia.org/wikipedia/en/thumb/d/d3/Logo_of_the_Bulgarian_Socialist_Party.svg/250px-Logo_of_the_Bulgarian_Socialist_Party.svg.png</t>
   </si>
   <si>
-    <t>Progressive Bulgaria</t>
-  </si>
-  <si>
-    <t>PB</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Progressive_Bulgaria.svg/960px-Progressive_Bulgaria.svg.png</t>
-  </si>
-  <si>
     <t>#D7171E</t>
   </si>
   <si>
@@ -416,12 +422,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/54/HDZ_logo.svg/330px-HDZ_logo.svg.png</t>
   </si>
   <si>
-    <t>#204A41</t>
-  </si>
-  <si>
-    <t>Non-Inscrits</t>
-  </si>
-  <si>
     <t>#295BA5</t>
   </si>
   <si>
@@ -545,6 +545,15 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3d/Member_of_the_European_Parliament_Jaroslav_Knot.jpg/250px-Member_of_the_European_Parliament_Jaroslav_Knot.jpg</t>
   </si>
   <si>
+    <t>The Bridge</t>
+  </si>
+  <si>
+    <t>Most</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/9/99/Logo_of_the_Bridge_%28Croatia%29.svg/1920px-Logo_of_the_Bridge_%28Croatia%29.svg.png</t>
+  </si>
+  <si>
     <t>Civic Democratic Party</t>
   </si>
   <si>
@@ -560,27 +569,21 @@
     <t>TOP 09</t>
   </si>
   <si>
+    <t>#E85726</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Logo_of_the_TOP_09_%282021%29.svg/330px-Logo_of_the_TOP_09_%282021%29.svg.png</t>
   </si>
   <si>
-    <t>The Bridge</t>
-  </si>
-  <si>
     <t>#993366</t>
   </si>
   <si>
-    <t>Most</t>
-  </si>
-  <si>
     <t>KDU-ČSL</t>
   </si>
   <si>
     <t>Lidovci</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/thumb/9/99/Logo_of_the_Bridge_%28Croatia%29.svg/1920px-Logo_of_the_Bridge_%28Croatia%29.svg.png</t>
-  </si>
-  <si>
     <t>https://i.ibb.co/MDFkRN5N/677842342-1319352330055443-3419458753781349884-n.png</t>
   </si>
   <si>
@@ -596,9 +599,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/1719998876279_20240703_BARTUSEK_Nikola_CZ_013.jpg/250px-1719998876279_20240703_BARTUSEK_Nikola_CZ_013.jpg</t>
   </si>
   <si>
-    <t>#E85726</t>
-  </si>
-  <si>
     <t>Motorists for Themselves</t>
   </si>
   <si>
@@ -956,6 +956,15 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Renaissance_parti_logo.svg/250px-Renaissance_parti_logo.svg.png</t>
   </si>
   <si>
+    <t>Conservative People's Party of Estonia</t>
+  </si>
+  <si>
+    <t>EKRE</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/a/a1/Conservative_People%27s_Party_of_Estonia_logo.svg/960px-Conservative_People%27s_Party_of_Estonia_logo.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;_=20211222000409</t>
+  </si>
+  <si>
     <t>#FFD600</t>
   </si>
   <si>
@@ -968,21 +977,15 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/1718798798373_20240618_GUETTA_Bernard_FR_004.jpg/250px-1718798798373_20240618_GUETTA_Bernard_FR_004.jpg</t>
   </si>
   <si>
-    <t>Conservative People's Party of Estonia</t>
-  </si>
-  <si>
-    <t>EKRE</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/thumb/a/a1/Conservative_People%27s_Party_of_Estonia_logo.svg/960px-Conservative_People%27s_Party_of_Estonia_logo.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;_=20211222000409</t>
-  </si>
-  <si>
     <t>Grégory Allione</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e0/1718798679783_20240618_ALLIONE_Gregory_FR_009.jpg/250px-1718798679783_20240618_ALLIONE_Gregory_FR_009.jpg</t>
   </si>
   <si>
+    <t>#0163AF</t>
+  </si>
+  <si>
     <t>Democratic Movement</t>
   </si>
   <si>
@@ -992,9 +995,6 @@
     <t>https://i.ibb.co/tTsRPDT5/logo-modem.png</t>
   </si>
   <si>
-    <t>#0163AF</t>
-  </si>
-  <si>
     <t>#ef5327</t>
   </si>
   <si>
@@ -1460,6 +1460,9 @@
     <t>https://i.ibb.co/SDdCjRSf/Logo-of-the-Our-Homeland-Movement.png</t>
   </si>
   <si>
+    <t>Panhellenic Socialist Movement  – Movement for Change</t>
+  </si>
+  <si>
     <t>#688D1B</t>
   </si>
   <si>
@@ -1475,12 +1478,15 @@
     <t>https://i.ibb.co/jZDxVkGc/Fianna-F-il-logo-2024.png</t>
   </si>
   <si>
+    <t>Greek Left Coalition</t>
+  </si>
+  <si>
+    <t>ELAS</t>
+  </si>
+  <si>
     <t>#66BB66</t>
   </si>
   <si>
-    <t>Panhellenic Socialist Movement  – Movement for Change</t>
-  </si>
-  <si>
     <t>Fine Gael</t>
   </si>
   <si>
@@ -1496,12 +1502,6 @@
     <t>Sinn Féin</t>
   </si>
   <si>
-    <t>Greek Left Coalition</t>
-  </si>
-  <si>
-    <t>ELAS</t>
-  </si>
-  <si>
     <t>https://i.ibb.co/23dn4cnd/path1145.png</t>
   </si>
   <si>
@@ -1556,15 +1556,15 @@
     <t>https://upload.wikimedia.org/wikipedia/en/d/d6/Hope_for_Democracy.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
+    <t>Brothers of Italy</t>
+  </si>
+  <si>
+    <t>FdI</t>
+  </si>
+  <si>
     <t>#E1B959</t>
   </si>
   <si>
-    <t>Brothers of Italy</t>
-  </si>
-  <si>
-    <t>FdI</t>
-  </si>
-  <si>
     <t>Italy</t>
   </si>
   <si>
@@ -1625,210 +1625,210 @@
     <t>https://i.ibb.co/4nh8PxGx/13.png</t>
   </si>
   <si>
+    <t>#FFEB3B</t>
+  </si>
+  <si>
+    <t>Forza Italia</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/JjSHqNS4/14.png</t>
+  </si>
+  <si>
+    <t>#0087DC</t>
+  </si>
+  <si>
+    <t>Lega per Salvini Premier</t>
+  </si>
+  <si>
+    <t>Lega</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/kss8TvGy/12.png</t>
+  </si>
+  <si>
+    <t>#008000</t>
+  </si>
+  <si>
+    <t>National Future</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/h1VcM9N1/Futuro-Nazionale-logo.png</t>
+  </si>
+  <si>
+    <t>#20293D</t>
+  </si>
+  <si>
+    <t>Green Europe</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/WWN3LG4N/19.png</t>
+  </si>
+  <si>
+    <t>#57B35D</t>
+  </si>
+  <si>
+    <t>Italian Left</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/k6xqXt8w/20.png</t>
+  </si>
+  <si>
+    <t>#FE1A33</t>
+  </si>
+  <si>
+    <t>South Tyrolean People's Party</t>
+  </si>
+  <si>
+    <t>SVP</t>
+  </si>
+  <si>
     <t>Soc Dems</t>
   </si>
   <si>
+    <t>https://i.ibb.co/P8n5n4G/29.png</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d8/Social_Democrats_%28Ireland%29_logo.svg/960px-Social_Democrats_%28Ireland%29_logo.svg.png</t>
   </si>
   <si>
-    <t>#FFEB3B</t>
-  </si>
-  <si>
-    <t>Forza Italia</t>
-  </si>
-  <si>
-    <t>FI</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/JjSHqNS4/14.png</t>
+    <t>#231F20</t>
+  </si>
+  <si>
+    <t>New Unity</t>
+  </si>
+  <si>
+    <t>JV</t>
+  </si>
+  <si>
+    <t>Latvia</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/k21R627H/3.png</t>
+  </si>
+  <si>
+    <t>#73b845</t>
+  </si>
+  <si>
+    <t>National Alliance</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/993s7rSf/15.png</t>
   </si>
   <si>
     <t>#752F8B</t>
   </si>
   <si>
-    <t>#0087DC</t>
-  </si>
-  <si>
-    <t>Lega per Salvini Premier</t>
-  </si>
-  <si>
-    <t>Lega</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/kss8TvGy/12.png</t>
-  </si>
-  <si>
-    <t>#008000</t>
-  </si>
-  <si>
-    <t>National Future</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/h1VcM9N1/Futuro-Nazionale-logo.png</t>
-  </si>
-  <si>
-    <t>#20293D</t>
-  </si>
-  <si>
-    <t>Green Europe</t>
-  </si>
-  <si>
-    <t>EV</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/WWN3LG4N/19.png</t>
-  </si>
-  <si>
-    <t>#57B35D</t>
-  </si>
-  <si>
-    <t>Italian Left</t>
+    <t>#932330</t>
+  </si>
+  <si>
+    <t>For Latvia's Development</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/7d41t6d2/3ilwip-U2-400x400.png</t>
+  </si>
+  <si>
+    <t>#a2a2a2</t>
+  </si>
+  <si>
+    <t>United List</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/21ktVsB2/11.png</t>
+  </si>
+  <si>
+    <t>#ffa800</t>
+  </si>
+  <si>
+    <t>The Progressives</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/prZWzv9c/Platforma-logo.png</t>
+  </si>
+  <si>
+    <t>#F93B1D</t>
+  </si>
+  <si>
+    <t>Social Democratic Party "Harmony"</t>
+  </si>
+  <si>
+    <t>Saskaņa</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/Q3gs8gMM/417406814-897587372373097-6051379660106823097-n.png</t>
+  </si>
+  <si>
+    <t>#EA1B23</t>
+  </si>
+  <si>
+    <t>Latvia First</t>
+  </si>
+  <si>
+    <t>LPV</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Latvia_First_1%21_logo.png/250px-Latvia_First_1%21_logo.png</t>
   </si>
   <si>
     <t>Unity</t>
   </si>
   <si>
-    <t>SI</t>
-  </si>
-  <si>
     <t>Aontú</t>
   </si>
   <si>
-    <t>https://i.ibb.co/k6xqXt8w/20.png</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/en/7/77/Aont%C3%BA_logo.png</t>
   </si>
   <si>
-    <t>#FE1A33</t>
-  </si>
-  <si>
-    <t>South Tyrolean People's Party</t>
-  </si>
-  <si>
-    <t>SVP</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/P8n5n4G/29.png</t>
+    <t>#A8343C</t>
+  </si>
+  <si>
+    <t>Homeland Union</t>
+  </si>
+  <si>
+    <t>TS–LKD</t>
+  </si>
+  <si>
+    <t>Lithuania</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/b/b3/Homeland_Union_–_Lithuanian_Christian_Democrats.svg/330px-Homeland_Union_–_Lithuanian_Christian_Democrats.svg.png</t>
+  </si>
+  <si>
+    <t>#00A59B</t>
+  </si>
+  <si>
+    <t>Social Democratic Party of Lithuania</t>
+  </si>
+  <si>
+    <t>LSDP</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/zV1gWpRC/LSDP-logo.png</t>
   </si>
   <si>
     <t>#44532A</t>
   </si>
   <si>
-    <t>#231F20</t>
-  </si>
-  <si>
-    <t>New Unity</t>
-  </si>
-  <si>
-    <t>JV</t>
-  </si>
-  <si>
-    <t>Latvia</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/k21R627H/3.png</t>
-  </si>
-  <si>
-    <t>#73b845</t>
-  </si>
-  <si>
-    <t>National Alliance</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/993s7rSf/15.png</t>
-  </si>
-  <si>
-    <t>#932330</t>
-  </si>
-  <si>
-    <t>For Latvia's Development</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/7d41t6d2/3ilwip-U2-400x400.png</t>
-  </si>
-  <si>
-    <t>#a2a2a2</t>
-  </si>
-  <si>
-    <t>United List</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/21ktVsB2/11.png</t>
-  </si>
-  <si>
-    <t>#ffa800</t>
-  </si>
-  <si>
-    <t>The Progressives</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/prZWzv9c/Platforma-logo.png</t>
-  </si>
-  <si>
-    <t>#F93B1D</t>
-  </si>
-  <si>
-    <t>Social Democratic Party "Harmony"</t>
-  </si>
-  <si>
-    <t>Saskaņa</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/Q3gs8gMM/417406814-897587372373097-6051379660106823097-n.png</t>
-  </si>
-  <si>
-    <t>#EA1B23</t>
-  </si>
-  <si>
-    <t>Latvia First</t>
-  </si>
-  <si>
-    <t>LPV</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Latvia_First_1%21_logo.png/250px-Latvia_First_1%21_logo.png</t>
-  </si>
-  <si>
-    <t>#A8343C</t>
-  </si>
-  <si>
-    <t>Homeland Union</t>
-  </si>
-  <si>
-    <t>TS–LKD</t>
-  </si>
-  <si>
-    <t>Lithuania</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/thumb/b/b3/Homeland_Union_–_Lithuanian_Christian_Democrats.svg/330px-Homeland_Union_–_Lithuanian_Christian_Democrats.svg.png</t>
-  </si>
-  <si>
-    <t>#00A59B</t>
-  </si>
-  <si>
-    <t>Social Democratic Party of Lithuania</t>
-  </si>
-  <si>
-    <t>LSDP</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/zV1gWpRC/LSDP-logo.png</t>
-  </si>
-  <si>
     <t>#E10514</t>
   </si>
   <si>
@@ -1901,6 +1901,9 @@
     <t>https://i.ibb.co/v4kfT7g1/Untitled-design-7.png</t>
   </si>
   <si>
+    <t>League</t>
+  </si>
+  <si>
     <t>#F29402</t>
   </si>
   <si>
@@ -1937,37 +1940,118 @@
     <t>https://i.ibb.co/zT4fTq7S/Demokratesch-Partei.png</t>
   </si>
   <si>
+    <t>#002C4F</t>
+  </si>
+  <si>
+    <t>The Greens</t>
+  </si>
+  <si>
+    <t>Gréng</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/BKf4czM7/logo-15.png</t>
+  </si>
+  <si>
+    <t>#8EB74A</t>
+  </si>
+  <si>
+    <t>Alternative Democratic Reform Party</t>
+  </si>
+  <si>
+    <t>ADR</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Logo_of_the_Alternative_Democratic_Reform_Party_%282022%29.svg/330px-Logo_of_the_Alternative_Democratic_Reform_Party_%282022%29.svg.png</t>
+  </si>
+  <si>
+    <t>#00ADDC</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>Malta</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/SwL4wqdB/Logo-of-the-Labour-Party-Malta.png</t>
+  </si>
+  <si>
+    <t>#EE3224</t>
+  </si>
+  <si>
+    <t>Nationalist Party</t>
+  </si>
+  <si>
+    <t>PN</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/VWqPFc7G/pn-default.png</t>
+  </si>
+  <si>
+    <t>#005D9B</t>
+  </si>
+  <si>
+    <t>Progressive Netherlands</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/Ppm8qzJ/Progressive-Netherlands-logo.png</t>
+  </si>
+  <si>
+    <t>#ff0000</t>
+  </si>
+  <si>
+    <t>Party for Freedom</t>
+  </si>
+  <si>
+    <t>PVV</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/7/76/Party_for_Freedom_logo.svg/330px-Party_for_Freedom_logo.svg.png</t>
+  </si>
+  <si>
     <t>Sovereign Power</t>
   </si>
   <si>
     <t xml:space="preserve">SV </t>
   </si>
   <si>
+    <t>#234672</t>
+  </si>
+  <si>
+    <t>People's Party for Freedom and Democracy</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Suver%C4%93n%C4%81_vara_2024.svg/960px-Suver%C4%93n%C4%81_vara_2024.svg.png</t>
   </si>
   <si>
-    <t>#002C4F</t>
-  </si>
-  <si>
-    <t>The Greens</t>
-  </si>
-  <si>
-    <t>Gréng</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/BKf4czM7/logo-15.png</t>
-  </si>
-  <si>
-    <t>#8EB74A</t>
-  </si>
-  <si>
-    <t>Alternative Democratic Reform Party</t>
-  </si>
-  <si>
-    <t>ADR</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Logo_of_the_Alternative_Democratic_Reform_Party_%282022%29.svg/330px-Logo_of_the_Alternative_Democratic_Reform_Party_%282022%29.svg.png</t>
+    <t>VVD</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7a/VVD_logo_%282020–present%29.svg/250px-VVD_logo_%282020–present%29.svg.png</t>
+  </si>
+  <si>
+    <t>#0328CB</t>
+  </si>
+  <si>
+    <t>Christian Democratic Appeal</t>
+  </si>
+  <si>
+    <t>CDA</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/CDA_logo_2021.svg/250px-CDA_logo_2021.svg.png</t>
+  </si>
+  <si>
+    <t>#1F9359</t>
+  </si>
+  <si>
+    <t>Democrats 66</t>
+  </si>
+  <si>
+    <t>D66</t>
   </si>
   <si>
     <t>#6767AB</t>
@@ -1982,33 +2066,30 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Latvia_road_sign_330.svg/960px-Latvia_road_sign_330.svg.png</t>
   </si>
   <si>
-    <t>#00ADDC</t>
-  </si>
-  <si>
-    <t>PL</t>
-  </si>
-  <si>
-    <t>Malta</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/SwL4wqdB/Logo-of-the-Labour-Party-Malta.png</t>
-  </si>
-  <si>
-    <t>#EE3224</t>
-  </si>
-  <si>
-    <t>Nationalist Party</t>
-  </si>
-  <si>
-    <t>PN</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e9/D66_logo_%282019–present%29.svg/330px-D66_logo_%282019–present%29.svg.png</t>
+  </si>
+  <si>
+    <t>#00AE41</t>
+  </si>
+  <si>
+    <t>Farmer–Citizen Movement</t>
+  </si>
+  <si>
+    <t>BBB</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/BoerBurgerBeweging_logo.svg/330px-BoerBurgerBeweging_logo.svg.png</t>
+  </si>
+  <si>
+    <t>#95C11F</t>
+  </si>
+  <si>
+    <t>Volt Netherlands</t>
   </si>
   <si>
     <t>#19191E</t>
   </si>
   <si>
-    <t>https://i.ibb.co/VWqPFc7G/pn-default.png</t>
-  </si>
-  <si>
     <t>Union of Greens and Farmers</t>
   </si>
   <si>
@@ -2018,108 +2099,30 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/Za%C4%BCo_un_Zemnieku_savien%C4%ABba_Logo.svg/1920px-Za%C4%BCo_un_Zemnieku_savien%C4%ABba_Logo.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>#005D9B</t>
-  </si>
-  <si>
-    <t>Progressive Netherlands</t>
-  </si>
-  <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/Ppm8qzJ/Progressive-Netherlands-logo.png</t>
-  </si>
-  <si>
-    <t>#ff0000</t>
+    <t>Party for the Animals</t>
+  </si>
+  <si>
+    <t>PvdD</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/m53wFmSx/Party-for-the-Animals-logo.png</t>
+  </si>
+  <si>
+    <t>#00743C</t>
+  </si>
+  <si>
+    <t>New Social Contract</t>
+  </si>
+  <si>
+    <t>NSC</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/db/NSC_partijlogo.svg/330px-NSC_partijlogo.svg.png</t>
   </si>
   <si>
     <t>#03723A</t>
   </si>
   <si>
-    <t>Party for Freedom</t>
-  </si>
-  <si>
-    <t>PVV</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/thumb/7/76/Party_for_Freedom_logo.svg/330px-Party_for_Freedom_logo.svg.png</t>
-  </si>
-  <si>
-    <t>#234672</t>
-  </si>
-  <si>
-    <t>People's Party for Freedom and Democracy</t>
-  </si>
-  <si>
-    <t>VVD</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7a/VVD_logo_%282020–present%29.svg/250px-VVD_logo_%282020–present%29.svg.png</t>
-  </si>
-  <si>
-    <t>#0328CB</t>
-  </si>
-  <si>
-    <t>Christian Democratic Appeal</t>
-  </si>
-  <si>
-    <t>CDA</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/CDA_logo_2021.svg/250px-CDA_logo_2021.svg.png</t>
-  </si>
-  <si>
-    <t>#1F9359</t>
-  </si>
-  <si>
-    <t>Democrats 66</t>
-  </si>
-  <si>
-    <t>D66</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e9/D66_logo_%282019–present%29.svg/330px-D66_logo_%282019–present%29.svg.png</t>
-  </si>
-  <si>
-    <t>#00AE41</t>
-  </si>
-  <si>
-    <t>Farmer–Citizen Movement</t>
-  </si>
-  <si>
-    <t>BBB</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/BoerBurgerBeweging_logo.svg/330px-BoerBurgerBeweging_logo.svg.png</t>
-  </si>
-  <si>
-    <t>#95C11F</t>
-  </si>
-  <si>
-    <t>Volt Netherlands</t>
-  </si>
-  <si>
-    <t>Party for the Animals</t>
-  </si>
-  <si>
-    <t>PvdD</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/m53wFmSx/Party-for-the-Animals-logo.png</t>
-  </si>
-  <si>
-    <t>#00743C</t>
-  </si>
-  <si>
-    <t>New Social Contract</t>
-  </si>
-  <si>
-    <t>NSC</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/db/NSC_partijlogo.svg/330px-NSC_partijlogo.svg.png</t>
-  </si>
-  <si>
     <t>#F0C400</t>
   </si>
   <si>
@@ -2147,22 +2150,79 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a6/Logo_Koalicja_Obywatelska_2023_serce.svg/330px-Logo_Koalicja_Obywatelska_2023_serce.svg.png</t>
   </si>
   <si>
+    <t>#F68F2D</t>
+  </si>
+  <si>
+    <t>Law and Justice</t>
+  </si>
+  <si>
+    <t>PiS</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/2/2a/Logo_of_the_Law_and_Justice.svg/250px-Logo_of_the_Law_and_Justice.svg.png</t>
+  </si>
+  <si>
+    <t>#073A76</t>
+  </si>
+  <si>
+    <t>Development Plus</t>
+  </si>
+  <si>
+    <t>R+</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/5hrjXQQD/Rozw-j-Plus.png</t>
+  </si>
+  <si>
+    <t>#75BAFF</t>
+  </si>
+  <si>
+    <t>National Movement</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/zTYWnbx2/National-Movement-Poland-logo.png</t>
+  </si>
+  <si>
+    <t>#CF1020</t>
+  </si>
+  <si>
+    <t>New Hope</t>
+  </si>
+  <si>
+    <t>NN</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/gMX6N71Q/Nowa-Nadzieja.png</t>
+  </si>
+  <si>
+    <t>#E8B909</t>
+  </si>
+  <si>
+    <t>Confederation of the Polish Crown</t>
+  </si>
+  <si>
+    <t>KKP</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Confederation_of_the_Polish_Crown_logo_%28shield_cropped%29.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">DP </t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7f/Darbo_Partija_Logo.svg/1280px-Darbo_Partija_Logo.svg.png</t>
   </si>
   <si>
-    <t>#F68F2D</t>
-  </si>
-  <si>
-    <t>Law and Justice</t>
-  </si>
-  <si>
-    <t>PiS</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/thumb/2/2a/Logo_of_the_Law_and_Justice.svg/250px-Logo_of_the_Law_and_Justice.svg.png</t>
+    <t>#A37919</t>
+  </si>
+  <si>
+    <t>Polish People's Party</t>
+  </si>
+  <si>
+    <t>PSL</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/Logo_of_the_Polish_People%27s_Party_%282019_color%29_%28four-leaf_clover_cropped%29.svg/250px-Logo_of_the_Polish_People%27s_Party_%282019_color%29_%28four-leaf_clover_cropped%29.svg.png</t>
   </si>
   <si>
     <t>#1E578C</t>
@@ -2174,87 +2234,36 @@
     <t>https://upload.wikimedia.org/wikipedia/en/thumb/c/c9/Logo_of_the_Dawn_of_Nemunas.svg/960px-Logo_of_the_Dawn_of_Nemunas.svg.png</t>
   </si>
   <si>
-    <t>#073A76</t>
-  </si>
-  <si>
-    <t>Development Plus</t>
-  </si>
-  <si>
-    <t>R+</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/5hrjXQQD/Rozw-j-Plus.png</t>
-  </si>
-  <si>
-    <t>#75BAFF</t>
-  </si>
-  <si>
-    <t>National Movement</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/zTYWnbx2/National-Movement-Poland-logo.png</t>
-  </si>
-  <si>
-    <t>#CF1020</t>
-  </si>
-  <si>
-    <t>New Hope</t>
+    <t>#2ED397</t>
+  </si>
+  <si>
+    <t>New Left</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/20/Lewica_01.svg/330px-Lewica_01.svg.png</t>
+  </si>
+  <si>
+    <t>#AC145A</t>
   </si>
   <si>
     <t>#F25D23</t>
   </si>
   <si>
-    <t>NN</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/gMX6N71Q/Nowa-Nadzieja.png</t>
-  </si>
-  <si>
-    <t>#E8B909</t>
-  </si>
-  <si>
-    <t>Confederation of the Polish Crown</t>
-  </si>
-  <si>
-    <t>KKP</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Confederation_of_the_Polish_Crown_logo_%28shield_cropped%29.png</t>
-  </si>
-  <si>
-    <t>#A37919</t>
-  </si>
-  <si>
-    <t>Polish People's Party</t>
-  </si>
-  <si>
-    <t>PSL</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/Logo_of_the_Polish_People%27s_Party_%282019_color%29_%28four-leaf_clover_cropped%29.svg/250px-Logo_of_the_Polish_People%27s_Party_%282019_color%29_%28four-leaf_clover_cropped%29.svg.png</t>
-  </si>
-  <si>
-    <t>#2ED397</t>
-  </si>
-  <si>
-    <t>New Left</t>
-  </si>
-  <si>
-    <t>NL</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/20/Lewica_01.svg/330px-Lewica_01.svg.png</t>
-  </si>
-  <si>
-    <t>#AC145A</t>
-  </si>
-  <si>
     <t>Centre Union</t>
   </si>
   <si>
+    <t>NS</t>
+  </si>
+  <si>
     <t>UC</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/NS-logotipas.svg/1280px-NS-logotipas.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/en/d/de/Centrum_parliamentary_circle_logo.png</t>
   </si>
   <si>
@@ -2270,6 +2279,9 @@
     <t>Portugal</t>
   </si>
   <si>
+    <t>#B81E23</t>
+  </si>
+  <si>
     <t>https://i.ibb.co/JwFWdv6C/Partido-Socialista-logo.png</t>
   </si>
   <si>
@@ -2432,37 +2444,61 @@
     <t>https://i.ibb.co/NdBJ764Q/PMP-logo.png</t>
   </si>
   <si>
+    <t>#A7CF35</t>
+  </si>
+  <si>
+    <t>S.O.S. Romania</t>
+  </si>
+  <si>
+    <t>SOS RO</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/SOS_Romania_logo.svg/250px-SOS_Romania_logo.svg.png</t>
+  </si>
+  <si>
+    <t>#4DA9DA</t>
+  </si>
+  <si>
+    <t>Romanian National Conservative Party</t>
+  </si>
+  <si>
+    <t>PNCR</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/TxTs73X2/Logo-of-the-Romanian-National-Conservative-Party.png</t>
+  </si>
+  <si>
     <t>Right Answer 21</t>
   </si>
   <si>
     <t>JA21</t>
   </si>
   <si>
-    <t>#A7CF35</t>
-  </si>
-  <si>
-    <t>S.O.S. Romania</t>
-  </si>
-  <si>
-    <t>SOS RO</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/JA21_logo.svg/960px-JA21_logo.svg.png</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/SOS_Romania_logo.svg/250px-SOS_Romania_logo.svg.png</t>
-  </si>
-  <si>
-    <t>#4DA9DA</t>
-  </si>
-  <si>
-    <t>Romanian National Conservative Party</t>
-  </si>
-  <si>
-    <t>PNCR</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/TxTs73X2/Logo-of-the-Romanian-National-Conservative-Party.png</t>
+    <t>#1665FE</t>
+  </si>
+  <si>
+    <t>Social Liberal Humanist Party</t>
+  </si>
+  <si>
+    <t>PUSL</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/dsMtscf4/Logo-balanta-site-bold-t-1-1.png</t>
+  </si>
+  <si>
+    <t>#1B6AB4</t>
+  </si>
+  <si>
+    <t>Health Education Nature Sustainability Party</t>
+  </si>
+  <si>
+    <t>SENS</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/51/SENS_logo.svg/330px-SENS_logo.svg.png</t>
   </si>
   <si>
     <t>#1F2756</t>
@@ -2477,16 +2513,16 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/FVD_logo.svg/1920px-FVD_logo.svg.png</t>
   </si>
   <si>
-    <t>#1665FE</t>
-  </si>
-  <si>
-    <t>Social Liberal Humanist Party</t>
-  </si>
-  <si>
-    <t>PUSL</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/dsMtscf4/Logo-balanta-site-bold-t-1-1.png</t>
+    <t>#A2DA5A</t>
+  </si>
+  <si>
+    <t>Progressive Slovakia</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Logo_of_the_Progressive_Slovakia_%282021%29.svg/250px-Logo_of_the_Progressive_Slovakia_%282021%29.svg.png</t>
   </si>
   <si>
     <t>#A71C20</t>
@@ -2498,51 +2534,27 @@
     <t>50+</t>
   </si>
   <si>
-    <t>#1B6AB4</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ec/50PLUS_%28nl%29_Logo.svg/1280px-50PLUS_%28nl%29_Logo.svg.png</t>
   </si>
   <si>
-    <t>Health Education Nature Sustainability Party</t>
-  </si>
-  <si>
-    <t>SENS</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/51/SENS_logo.svg/330px-SENS_logo.svg.png</t>
-  </si>
-  <si>
-    <t>#A2DA5A</t>
+    <t>#00BFFF</t>
+  </si>
+  <si>
+    <t>Direction – Social Democracy</t>
+  </si>
+  <si>
+    <t>Smer</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/RGwNfChp/Logo-of-the-Direction-Slovak-Social-Democracy.png</t>
+  </si>
+  <si>
+    <t>#D82222</t>
   </si>
   <si>
     <t>#92107D</t>
   </si>
   <si>
-    <t>Progressive Slovakia</t>
-  </si>
-  <si>
-    <t>Slovakia</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Logo_of_the_Progressive_Slovakia_%282021%29.svg/250px-Logo_of_the_Progressive_Slovakia_%282021%29.svg.png</t>
-  </si>
-  <si>
-    <t>#00BFFF</t>
-  </si>
-  <si>
-    <t>Direction – Social Democracy</t>
-  </si>
-  <si>
-    <t>Smer</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/RGwNfChp/Logo-of-the-Direction-Slovak-Social-Democracy.png</t>
-  </si>
-  <si>
-    <t>#D82222</t>
-  </si>
-  <si>
     <t>Republic Movement</t>
   </si>
   <si>
@@ -2609,42 +2621,42 @@
     <t>PVP</t>
   </si>
   <si>
+    <t>https://i.ibb.co/4RpkHgVy/Prerod.png</t>
+  </si>
+  <si>
+    <t>#6E288F</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8f/Socialni_demokrati_Logo.svg/250px-Socialni_demokrati_Logo.svg.png</t>
+  </si>
+  <si>
+    <t>#DD0000</t>
+  </si>
+  <si>
+    <t>New Slovenia – Christian Democrats</t>
+  </si>
+  <si>
+    <t>NSi</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/84/Nova_Slovenija_Logo.svg/330px-Nova_Slovenija_Logo.svg.png</t>
+  </si>
+  <si>
+    <t>#1DACD6</t>
+  </si>
+  <si>
+    <t>People's Party</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/23/1718288389061_20240611_KOBOSKO_Michal_PL_004.jpg/250px-1718288389061_20240611_KOBOSKO_Michal_PL_004.jpg</t>
   </si>
   <si>
-    <t>https://i.ibb.co/4RpkHgVy/Prerod.png</t>
-  </si>
-  <si>
-    <t>#6E288F</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8f/Socialni_demokrati_Logo.svg/250px-Socialni_demokrati_Logo.svg.png</t>
-  </si>
-  <si>
-    <t>#DD0000</t>
-  </si>
-  <si>
-    <t>New Slovenia – Christian Democrats</t>
-  </si>
-  <si>
-    <t>NSi</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/84/Nova_Slovenija_Logo.svg/330px-Nova_Slovenija_Logo.svg.png</t>
-  </si>
-  <si>
-    <t>#1DACD6</t>
-  </si>
-  <si>
-    <t>People's Party</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3c/Logo_del_PP_%282022%29.svg/330px-Logo_del_PP_%282022%29.svg.png</t>
   </si>
   <si>
@@ -2681,6 +2693,39 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/VOX_logo.svg/330px-VOX_logo.svg.png</t>
   </si>
   <si>
+    <t>#5AC035</t>
+  </si>
+  <si>
+    <t>Podemos</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Logo_de_Podemos_%282022%29.svg/330px-Logo_de_Podemos_%282022%29.svg.png</t>
+  </si>
+  <si>
+    <t>#9269F5</t>
+  </si>
+  <si>
+    <t>Sumar Movement</t>
+  </si>
+  <si>
+    <t>Sumar</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/16/Sumar_icon.svg/250px-Sumar_icon.svg.png</t>
+  </si>
+  <si>
+    <t>#E61455</t>
+  </si>
+  <si>
+    <t>Catalunya en Comú</t>
+  </si>
+  <si>
+    <t>Comuns</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/66/Comuns_Sumar_logo_sin_fondo.svg/250px-Comuns_Sumar_logo_sin_fondo.svg.png</t>
+  </si>
+  <si>
     <t>FREE</t>
   </si>
   <si>
@@ -2690,69 +2735,36 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e5/Logo_of_the_LIVRE.svg/960px-Logo_of_the_LIVRE.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>#5AC035</t>
-  </si>
-  <si>
-    <t>Podemos</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Logo_de_Podemos_%282022%29.svg/330px-Logo_de_Podemos_%282022%29.svg.png</t>
+    <t>#A6214B</t>
+  </si>
+  <si>
+    <t>Se Acabó La Fiesta</t>
+  </si>
+  <si>
+    <t>SALF</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/c/c4/Logo_of_the_Se_Acabó_La_Fiesta.png</t>
+  </si>
+  <si>
+    <t>#785A46</t>
+  </si>
+  <si>
+    <t>Diego Solier</t>
+  </si>
+  <si>
+    <t>Ind. ex-SALF</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/3YR8ZfTC/1720511557800-20240709-SOLIER-FERNANDEZ-Diego-ES-021.jpg</t>
+  </si>
+  <si>
+    <t>Nora Junco</t>
   </si>
   <si>
     <t>#C2D217</t>
   </si>
   <si>
-    <t>#9269F5</t>
-  </si>
-  <si>
-    <t>Sumar Movement</t>
-  </si>
-  <si>
-    <t>Sumar</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/16/Sumar_icon.svg/250px-Sumar_icon.svg.png</t>
-  </si>
-  <si>
-    <t>#E61455</t>
-  </si>
-  <si>
-    <t>Catalunya en Comú</t>
-  </si>
-  <si>
-    <t>Comuns</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/66/Comuns_Sumar_logo_sin_fondo.svg/250px-Comuns_Sumar_logo_sin_fondo.svg.png</t>
-  </si>
-  <si>
-    <t>#A6214B</t>
-  </si>
-  <si>
-    <t>Se Acabó La Fiesta</t>
-  </si>
-  <si>
-    <t>SALF</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/c/c4/Logo_of_the_Se_Acabó_La_Fiesta.png</t>
-  </si>
-  <si>
-    <t>#785A46</t>
-  </si>
-  <si>
-    <t>Diego Solier</t>
-  </si>
-  <si>
-    <t>Ind. ex-SALF</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/3YR8ZfTC/1720511557800-20240709-SOLIER-FERNANDEZ-Diego-ES-021.jpg</t>
-  </si>
-  <si>
-    <t>Nora Junco</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/1720511531541_20240709_JUNCO_GARCIA_Nora_ES_011.jpg/250px-1720511531541_20240709_JUNCO_GARCIA_Nora_ES_011.jpg</t>
   </si>
   <si>
@@ -2958,6 +2970,18 @@
   </si>
   <si>
     <t>#E82C25</t>
+  </si>
+  <si>
+    <t>Catalonia in Common</t>
+  </si>
+  <si>
+    <t>CatEnComú</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/Catalunya_en_Com%C3%BA_2024_%282%29_Logo.svg/1920px-Catalunya_en_Com%C3%BA_2024_%282%29_Logo.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>#AE355B</t>
   </si>
 </sst>
 </file>
@@ -3449,22 +3473,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1">
         <v>3.0</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>32</v>
@@ -3472,22 +3496,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C8" s="1">
         <v>3.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>12</v>
@@ -3495,19 +3519,19 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1">
         <v>3.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>48</v>
@@ -3527,7 +3551,7 @@
         <v>2.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>52</v>
@@ -3550,13 +3574,13 @@
         <v>2.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>17</v>
@@ -3564,19 +3588,19 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>62</v>
@@ -3596,7 +3620,7 @@
         <v>1.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>64</v>
@@ -3619,7 +3643,7 @@
         <v>1.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>68</v>
@@ -3628,7 +3652,7 @@
         <v>69</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -3642,7 +3666,7 @@
         <v>1.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>72</v>
@@ -3651,7 +3675,7 @@
         <v>73</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H15" s="3"/>
     </row>
@@ -3666,7 +3690,7 @@
         <v>1.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>76</v>
@@ -3689,7 +3713,7 @@
         <v>1.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>80</v>
@@ -3712,7 +3736,7 @@
         <v>1.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>83</v>
@@ -3735,7 +3759,7 @@
         <v>1.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>87</v>
@@ -3835,7 +3859,7 @@
         <v>104</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>49</v>
@@ -3843,10 +3867,10 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C24" s="1">
         <v>2.0</v>
@@ -3855,10 +3879,10 @@
         <v>91</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>32</v>
@@ -3867,10 +3891,10 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C25" s="1">
         <v>1.0</v>
@@ -3879,10 +3903,10 @@
         <v>91</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>17</v>
@@ -3891,10 +3915,10 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C26" s="1">
         <v>3.0</v>
@@ -3903,21 +3927,21 @@
         <v>91</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
@@ -3926,10 +3950,10 @@
         <v>91</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>22</v>
@@ -3938,10 +3962,10 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C28" s="1">
         <v>1.0</v>
@@ -3950,10 +3974,10 @@
         <v>91</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>49</v>
@@ -3962,19 +3986,19 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C29" s="1">
         <v>6.0</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>136</v>
@@ -3994,7 +4018,7 @@
         <v>4.0</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>139</v>
@@ -4018,7 +4042,7 @@
         <v>1.0</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>143</v>
@@ -4041,7 +4065,7 @@
         <v>1.0</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>146</v>
@@ -4097,7 +4121,7 @@
         <v>156</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35">
@@ -4120,7 +4144,7 @@
         <v>160</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36">
@@ -4219,10 +4243,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C40" s="1">
         <v>3.0</v>
@@ -4231,10 +4255,10 @@
         <v>171</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>49</v>
@@ -4243,10 +4267,10 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C41" s="1">
         <v>2.0</v>
@@ -4255,10 +4279,10 @@
         <v>171</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>17</v>
@@ -4266,10 +4290,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C42" s="1">
         <v>1.0</v>
@@ -4278,10 +4302,10 @@
         <v>171</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>17</v>
@@ -4290,10 +4314,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C43" s="1">
         <v>1.0</v>
@@ -4302,7 +4326,7 @@
         <v>171</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>73</v>
@@ -4355,7 +4379,7 @@
         <v>202</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46">
@@ -4378,7 +4402,7 @@
         <v>206</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47">
@@ -4447,7 +4471,7 @@
         <v>217</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50">
@@ -4608,7 +4632,7 @@
         <v>246</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57">
@@ -4815,7 +4839,7 @@
         <v>284</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66">
@@ -4977,7 +5001,7 @@
         <v>73</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H72" s="6"/>
     </row>
@@ -4998,7 +5022,7 @@
         <v>313</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>32</v>
@@ -5006,10 +5030,10 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C74" s="1">
         <v>1.0</v>
@@ -5018,7 +5042,7 @@
         <v>306</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>73</v>
@@ -5033,7 +5057,7 @@
         <v>321</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C75" s="1">
         <v>1.0</v>
@@ -5054,10 +5078,10 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C76" s="1">
         <v>3.0</v>
@@ -5066,7 +5090,7 @@
         <v>306</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>327</v>
@@ -5150,7 +5174,7 @@
         <v>338</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C80" s="1">
         <v>2.0</v>
@@ -5188,7 +5212,7 @@
         <v>344</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82">
@@ -5303,7 +5327,7 @@
         <v>364</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87">
@@ -5372,7 +5396,7 @@
         <v>376</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="90">
@@ -5441,7 +5465,7 @@
         <v>387</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="93">
@@ -5464,7 +5488,7 @@
         <v>73</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="94">
@@ -5510,7 +5534,7 @@
         <v>398</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96">
@@ -5579,7 +5603,7 @@
         <v>410</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H98" s="3"/>
     </row>
@@ -5626,7 +5650,7 @@
         <v>418</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="101">
@@ -5741,7 +5765,7 @@
         <v>439</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="106">
@@ -5764,7 +5788,7 @@
         <v>73</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="107">
@@ -5787,7 +5811,7 @@
         <v>446</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="108">
@@ -5833,7 +5857,7 @@
         <v>453</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="110">
@@ -5856,7 +5880,7 @@
         <v>457</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="111">
@@ -5991,30 +6015,30 @@
         <v>481</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C117" s="1">
         <v>4.0</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>32</v>
@@ -6022,22 +6046,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C118" s="1">
         <v>4.0</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>17</v>
@@ -6045,7 +6069,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>219</v>
@@ -6054,7 +6078,7 @@
         <v>2.0</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>496</v>
@@ -6063,7 +6087,7 @@
         <v>497</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="120">
@@ -6077,7 +6101,7 @@
         <v>1.0</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>500</v>
@@ -6100,7 +6124,7 @@
         <v>1.0</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>504</v>
@@ -6123,7 +6147,7 @@
         <v>1.0</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>508</v>
@@ -6132,7 +6156,7 @@
         <v>73</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123">
@@ -6146,7 +6170,7 @@
         <v>1.0</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>512</v>
@@ -6160,10 +6184,10 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="C124" s="1">
         <v>24.0</v>
@@ -6291,18 +6315,18 @@
         <v>536</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C130" s="1">
         <v>8.0</v>
@@ -6311,10 +6335,10 @@
         <v>517</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>17</v>
@@ -6322,10 +6346,10 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C131" s="1">
         <v>7.0</v>
@@ -6334,10 +6358,10 @@
         <v>517</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>12</v>
@@ -6345,10 +6369,10 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C132" s="1">
         <v>1.0</v>
@@ -6357,21 +6381,21 @@
         <v>517</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C133" s="1">
         <v>4.0</v>
@@ -6380,10 +6404,10 @@
         <v>517</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>27</v>
@@ -6391,10 +6415,10 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C134" s="1">
         <v>2.0</v>
@@ -6403,21 +6427,21 @@
         <v>517</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C135" s="1">
         <v>1.0</v>
@@ -6426,10 +6450,10 @@
         <v>517</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>17</v>
@@ -6437,22 +6461,22 @@
     </row>
     <row r="136">
       <c r="A136" s="3" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C136" s="1">
         <v>2.0</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>17</v>
@@ -6461,22 +6485,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C137" s="1">
         <v>2.0</v>
       </c>
       <c r="D137" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="E137" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="F137" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>49</v>
@@ -6484,7 +6508,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>248</v>
@@ -6493,13 +6517,13 @@
         <v>1.0</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>32</v>
@@ -6507,22 +6531,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C139" s="1">
         <v>1.0</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>49</v>
@@ -6530,22 +6554,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C140" s="1">
         <v>1.0</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>27</v>
@@ -6553,22 +6577,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C141" s="1">
         <v>1.0</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>22</v>
@@ -6576,22 +6600,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C142" s="1">
         <v>1.0</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E142" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>596</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>12</v>
@@ -6599,22 +6623,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B143" s="8" t="s">
         <v>597</v>
-      </c>
-      <c r="B143" s="8" t="s">
-        <v>598</v>
       </c>
       <c r="C143" s="1">
         <v>4.0</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="F143" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>17</v>
@@ -6622,19 +6646,19 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B144" s="7" t="s">
         <v>602</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>603</v>
       </c>
       <c r="C144" s="1">
         <v>2.0</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>605</v>
@@ -6654,7 +6678,7 @@
         <v>1.0</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>608</v>
@@ -6677,7 +6701,7 @@
         <v>1.0</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>612</v>
@@ -6700,7 +6724,7 @@
         <v>1.0</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>616</v>
@@ -6723,7 +6747,7 @@
         <v>1.0</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E148" s="5" t="s">
         <v>620</v>
@@ -6746,7 +6770,7 @@
         <v>1.0</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>624</v>
@@ -6755,7 +6779,7 @@
         <v>625</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H149" s="3"/>
     </row>
@@ -6770,13 +6794,13 @@
         <v>1.0</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>628</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>32</v>
@@ -6785,22 +6809,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C151" s="1">
         <v>3.0</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>17</v>
@@ -6808,22 +6832,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C152" s="1">
         <v>1.0</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>22</v>
@@ -6834,19 +6858,19 @@
         <v>165</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C153" s="1">
         <v>1.0</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>32</v>
@@ -6854,22 +6878,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="C154" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="F154" s="1" t="s">
         <v>646</v>
-      </c>
-      <c r="C154" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>648</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>27</v>
@@ -6877,22 +6901,22 @@
     </row>
     <row r="155">
       <c r="A155" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C155" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E155" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="F155" s="1" t="s">
         <v>650</v>
-      </c>
-      <c r="C155" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>656</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>49</v>
@@ -6904,19 +6928,19 @@
         <v>498</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="C156" s="1">
         <v>3.0</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>22</v>
@@ -6924,22 +6948,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C157" s="1">
         <v>3.0</v>
       </c>
       <c r="D157" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F157" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>668</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>17</v>
@@ -6947,22 +6971,22 @@
     </row>
     <row r="158">
       <c r="A158" s="6" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C158" s="1">
         <v>8.0</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>22</v>
@@ -6971,22 +6995,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="C159" s="1">
         <v>6.0</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>12</v>
@@ -6994,22 +7018,22 @@
     </row>
     <row r="160">
       <c r="A160" s="3" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="C160" s="1">
         <v>4.0</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>32</v>
@@ -7018,22 +7042,22 @@
     </row>
     <row r="161">
       <c r="A161" s="3" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="C161" s="1">
         <v>3.0</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>17</v>
@@ -7042,22 +7066,22 @@
     </row>
     <row r="162">
       <c r="A162" s="3" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="C162" s="9">
         <v>3.0</v>
       </c>
       <c r="D162" s="10" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>32</v>
@@ -7066,22 +7090,22 @@
     </row>
     <row r="163">
       <c r="A163" s="3" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C163" s="1">
         <v>2.0</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>49</v>
@@ -7090,7 +7114,7 @@
     </row>
     <row r="164">
       <c r="A164" s="3" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>404</v>
@@ -7099,7 +7123,7 @@
         <v>2.0</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>405</v>
@@ -7123,7 +7147,7 @@
         <v>1.0</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>697</v>
@@ -7132,7 +7156,7 @@
         <v>698</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="166">
@@ -7146,13 +7170,13 @@
         <v>1.0</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>701</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>17</v>
@@ -7160,22 +7184,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C167" s="1">
         <v>1.0</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>49</v>
@@ -7183,22 +7207,22 @@
     </row>
     <row r="168">
       <c r="A168" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C168" s="1">
         <v>21.0</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>17</v>
@@ -7207,22 +7231,22 @@
     </row>
     <row r="169">
       <c r="A169" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>715</v>
       </c>
       <c r="C169" s="1">
         <v>20.0</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E169" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="F169" s="1" t="s">
         <v>716</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>720</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>49</v>
@@ -7231,22 +7255,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="C170" s="1">
         <v>3.0</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>49</v>
@@ -7254,7 +7278,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>305</v>
@@ -7263,13 +7287,13 @@
         <v>2.0</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>12</v>
@@ -7277,67 +7301,67 @@
     </row>
     <row r="172">
       <c r="A172" s="3" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C172" s="1">
         <v>2.0</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H172" s="3"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C173" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="C173" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>736</v>
-      </c>
       <c r="G173" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H173" s="3"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C174" s="1">
         <v>2.0</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>740</v>
@@ -7358,7 +7382,7 @@
         <v>3.0</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>743</v>
@@ -7373,19 +7397,19 @@
     </row>
     <row r="176">
       <c r="A176" s="6" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C176" s="1">
         <v>1.0</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>73</v>
@@ -7397,19 +7421,19 @@
     </row>
     <row r="177">
       <c r="A177" s="6" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="C177" s="1">
         <v>1.0</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>73</v>
@@ -7430,13 +7454,13 @@
         <v>8.0</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>22</v>
@@ -7448,19 +7472,19 @@
         <v>264</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C179" s="1">
         <v>6.0</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>17</v>
@@ -7469,22 +7493,22 @@
     </row>
     <row r="180">
       <c r="A180" s="3" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C180" s="1">
         <v>1.0</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>17</v>
@@ -7493,22 +7517,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C181" s="1">
         <v>2.0</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>12</v>
@@ -7516,22 +7540,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C182" s="1">
         <v>2.0</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>32</v>
@@ -7539,48 +7563,48 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="C183" s="1">
         <v>1.0</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="C184" s="1">
         <v>1.0</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="185">
@@ -7588,19 +7612,19 @@
         <v>264</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C185" s="1">
         <v>11.0</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>22</v>
@@ -7608,22 +7632,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="C186" s="1">
         <v>8.0</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>17</v>
@@ -7631,22 +7655,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="C187" s="1">
         <v>3.0</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>49</v>
@@ -7654,22 +7678,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="C188" s="1">
         <v>3.0</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>49</v>
@@ -7677,22 +7701,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="C189" s="1">
         <v>2.0</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>32</v>
@@ -7700,22 +7724,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="C190" s="1">
         <v>2.0</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>17</v>
@@ -7723,7 +7747,7 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>424</v>
@@ -7732,36 +7756,36 @@
         <v>1.0</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="C192" s="1">
         <v>1.0</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>32</v>
@@ -7770,42 +7794,42 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C193" s="1">
         <v>1.0</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C194" s="1">
         <v>1.0</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>821</v>
@@ -7825,13 +7849,13 @@
         <v>1.0</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>824</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>22</v>
@@ -7839,19 +7863,19 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="C196" s="1">
         <v>1.0</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>833</v>
@@ -7862,7 +7886,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>297</v>
@@ -7871,13 +7895,13 @@
         <v>6.0</v>
       </c>
       <c r="D197" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="E197" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="E197" s="2" t="s">
-        <v>837</v>
-      </c>
       <c r="F197" s="1" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>32</v>
@@ -7885,91 +7909,91 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C198" s="1">
         <v>5.0</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="C199" s="1">
         <v>2.0</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="C200" s="1">
         <v>1.0</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="C201" s="1">
         <v>1.0</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>17</v>
@@ -7977,7 +8001,7 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>95</v>
@@ -7986,13 +8010,13 @@
         <v>4.0</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>17</v>
@@ -8000,22 +8024,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C203" s="1">
         <v>2.0</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>32</v>
@@ -8023,22 +8047,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C204" s="1">
         <v>1.0</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>27</v>
@@ -8049,19 +8073,19 @@
         <v>223</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C205" s="1">
         <v>1.0</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>22</v>
@@ -8069,22 +8093,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="B206" s="13" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="C206" s="1">
         <v>1.0</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>17</v>
@@ -8092,22 +8116,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C207" s="1">
         <v>22.0</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>17</v>
@@ -8115,22 +8139,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="C208" s="1">
         <v>18.0</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>22</v>
@@ -8138,22 +8162,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="C209" s="1">
         <v>2.0</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>22</v>
@@ -8161,22 +8185,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C210" s="1">
         <v>6.0</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>12</v>
@@ -8184,25 +8208,25 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C211" s="1">
         <v>2.0</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>896</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="212">
@@ -8216,7 +8240,7 @@
         <v>1.0</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>899</v>
@@ -8225,7 +8249,7 @@
         <v>900</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="213">
@@ -8239,13 +8263,13 @@
         <v>1.0</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>903</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>27</v>
@@ -8253,42 +8277,42 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C214" s="1">
         <v>1.0</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C215" s="1">
         <v>1.0</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>73</v>
@@ -8299,19 +8323,19 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="C216" s="1">
         <v>1.0</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>73</v>
@@ -8322,22 +8346,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="C217" s="1">
         <v>1.0</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>27</v>
@@ -8345,22 +8369,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C218" s="1">
         <v>1.0</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>27</v>
@@ -8368,45 +8392,45 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="C219" s="1">
         <v>1.0</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="C220" s="1">
         <v>1.0</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>27</v>
@@ -8414,22 +8438,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="C221" s="1">
         <v>1.0</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>32</v>
@@ -8437,22 +8461,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="C222" s="1">
         <v>1.0</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>32</v>
@@ -8460,22 +8484,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="C223" s="1">
         <v>5.0</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>22</v>
@@ -8483,7 +8507,7 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>256</v>
@@ -8492,13 +8516,13 @@
         <v>4.0</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>17</v>
@@ -8506,22 +8530,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="C225" s="1">
         <v>3.0</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>27</v>
@@ -8529,22 +8553,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C226" s="1">
         <v>3.0</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>49</v>
@@ -8552,7 +8576,7 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>228</v>
@@ -8561,16 +8585,16 @@
         <v>2.0</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="228">
@@ -8578,19 +8602,19 @@
         <v>288</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C228" s="1">
         <v>2.0</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>32</v>
@@ -8598,22 +8622,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C229" s="1">
         <v>2.0</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>17</v>
@@ -8621,22 +8645,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="C230" s="1">
         <v>1.0</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>32</v>
@@ -9018,10 +9042,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1">
         <v>1.0</v>
@@ -9030,33 +9054,33 @@
         <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1">
         <v>2.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
@@ -9064,22 +9088,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1">
         <v>4.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>12</v>
@@ -9087,19 +9111,19 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" s="1">
         <v>3.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>48</v>
@@ -9119,7 +9143,7 @@
         <v>2.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>52</v>
@@ -9142,13 +9166,13 @@
         <v>1.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>56</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>17</v>
@@ -9156,19 +9180,19 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>62</v>
@@ -9188,7 +9212,7 @@
         <v>1.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>64</v>
@@ -9211,7 +9235,7 @@
         <v>3.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>68</v>
@@ -9220,7 +9244,7 @@
         <v>69</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -9234,7 +9258,7 @@
         <v>0.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>72</v>
@@ -9243,7 +9267,7 @@
         <v>73</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H16" s="3"/>
     </row>
@@ -9258,7 +9282,7 @@
         <v>1.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>76</v>
@@ -9281,7 +9305,7 @@
         <v>2.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>80</v>
@@ -9304,7 +9328,7 @@
         <v>0.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>83</v>
@@ -9327,7 +9351,7 @@
         <v>1.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>87</v>
@@ -9341,10 +9365,10 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C21" s="1">
         <v>9.0</v>
@@ -9353,13 +9377,13 @@
         <v>91</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22">
@@ -9444,7 +9468,7 @@
         <v>104</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>49</v>
@@ -9452,22 +9476,22 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C26" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>32</v>
@@ -9476,22 +9500,22 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C27" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>17</v>
@@ -9500,39 +9524,39 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>22</v>
@@ -9541,19 +9565,19 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>91</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>49</v>
@@ -9562,19 +9586,19 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C31" s="1">
         <v>5.0</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>136</v>
@@ -9594,7 +9618,7 @@
         <v>4.0</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>139</v>
@@ -9615,7 +9639,7 @@
         <v>142</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>143</v>
@@ -9638,7 +9662,7 @@
         <v>2.0</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>146</v>
@@ -9652,22 +9676,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="C35" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>49</v>
@@ -9717,7 +9741,7 @@
         <v>156</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38">
@@ -9737,7 +9761,7 @@
         <v>160</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39">
@@ -9833,10 +9857,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C43" s="1">
         <v>4.0</v>
@@ -9845,10 +9869,10 @@
         <v>171</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>49</v>
@@ -9857,19 +9881,19 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>171</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>17</v>
@@ -9877,19 +9901,19 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>171</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>17</v>
@@ -9898,16 +9922,16 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>171</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>73</v>
@@ -9954,7 +9978,7 @@
         <v>202</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49">
@@ -9974,7 +9998,7 @@
         <v>206</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50">
@@ -10043,7 +10067,7 @@
         <v>217</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="53">
@@ -10100,7 +10124,7 @@
         <v>228</v>
       </c>
       <c r="C55" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>220</v>
@@ -10145,6 +10169,9 @@
       <c r="B57" s="1" t="s">
         <v>236</v>
       </c>
+      <c r="C57" s="1">
+        <v>1.0</v>
+      </c>
       <c r="D57" s="1" t="s">
         <v>220</v>
       </c>
@@ -10201,7 +10228,7 @@
         <v>246</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60">
@@ -10211,6 +10238,9 @@
       <c r="B60" s="1" t="s">
         <v>248</v>
       </c>
+      <c r="C60" s="1">
+        <v>1.0</v>
+      </c>
       <c r="D60" s="1" t="s">
         <v>220</v>
       </c>
@@ -10364,10 +10394,10 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C67" s="1">
         <v>1.0</v>
@@ -10376,10 +10406,10 @@
         <v>261</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>12</v>
@@ -10428,7 +10458,7 @@
         <v>284</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70">
@@ -10439,7 +10469,7 @@
         <v>138</v>
       </c>
       <c r="C70" s="1">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>278</v>
@@ -10508,7 +10538,7 @@
         <v>297</v>
       </c>
       <c r="C73" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>278</v>
@@ -10551,7 +10581,7 @@
         <v>305</v>
       </c>
       <c r="C75" s="1">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>306</v>
@@ -10584,7 +10614,7 @@
         <v>73</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H76" s="6"/>
     </row>
@@ -10596,7 +10626,7 @@
         <v>269</v>
       </c>
       <c r="C77" s="1">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>306</v>
@@ -10605,7 +10635,7 @@
         <v>313</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>32</v>
@@ -10613,16 +10643,16 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>306</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>73</v>
@@ -10637,7 +10667,7 @@
         <v>321</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>306</v>
@@ -10655,10 +10685,10 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C80" s="1">
         <v>4.0</v>
@@ -10667,7 +10697,7 @@
         <v>306</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>327</v>
@@ -10748,7 +10778,7 @@
         <v>338</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C84" s="1">
         <v>2.0</v>
@@ -10774,7 +10804,7 @@
         <v>342</v>
       </c>
       <c r="C85" s="1">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>306</v>
@@ -10786,7 +10816,7 @@
         <v>344</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86">
@@ -10797,7 +10827,7 @@
         <v>346</v>
       </c>
       <c r="C86" s="1">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>306</v>
@@ -10889,7 +10919,7 @@
         <v>364</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91">
@@ -10900,7 +10930,7 @@
         <v>366</v>
       </c>
       <c r="C91" s="1">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>367</v>
@@ -10923,7 +10953,7 @@
         <v>370</v>
       </c>
       <c r="C92" s="1">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>367</v>
@@ -10946,7 +10976,7 @@
         <v>374</v>
       </c>
       <c r="C93" s="1">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>367</v>
@@ -10958,7 +10988,7 @@
         <v>376</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="94">
@@ -11015,7 +11045,7 @@
         <v>385</v>
       </c>
       <c r="C96" s="1">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>367</v>
@@ -11027,7 +11057,7 @@
         <v>387</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="97">
@@ -11047,7 +11077,7 @@
         <v>73</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="98">
@@ -11058,7 +11088,7 @@
         <v>392</v>
       </c>
       <c r="C98" s="1">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>367</v>
@@ -11093,7 +11123,7 @@
         <v>398</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100">
@@ -11104,7 +11134,7 @@
         <v>400</v>
       </c>
       <c r="C100" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>367</v>
@@ -11159,7 +11189,7 @@
         <v>410</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H102" s="3"/>
     </row>
@@ -11203,7 +11233,7 @@
         <v>418</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="105">
@@ -11271,13 +11301,13 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>433</v>
       </c>
       <c r="C108" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>429</v>
@@ -11294,10 +11324,10 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C109" s="1">
         <v>4.0</v>
@@ -11312,7 +11342,7 @@
         <v>439</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="110">
@@ -11332,7 +11362,7 @@
         <v>73</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="111">
@@ -11355,7 +11385,7 @@
         <v>446</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="112">
@@ -11398,7 +11428,7 @@
         <v>453</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="114">
@@ -11421,7 +11451,7 @@
         <v>457</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115">
@@ -11464,10 +11494,10 @@
         <v>513</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="117">
@@ -11573,30 +11603,30 @@
         <v>481</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C122" s="1">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>32</v>
@@ -11604,22 +11634,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C123" s="1">
         <v>4.0</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>17</v>
@@ -11627,16 +11657,16 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>219</v>
       </c>
       <c r="C124" s="1">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>496</v>
@@ -11645,7 +11675,7 @@
         <v>497</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="125">
@@ -11656,7 +11686,7 @@
         <v>499</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>500</v>
@@ -11673,22 +11703,22 @@
         <v>223</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>537</v>
+        <v>560</v>
       </c>
       <c r="C126" s="1">
         <v>3.0</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127">
@@ -11698,8 +11728,11 @@
       <c r="B127" s="1" t="s">
         <v>503</v>
       </c>
+      <c r="C127" s="1">
+        <v>1.0</v>
+      </c>
       <c r="D127" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>504</v>
@@ -11719,7 +11752,7 @@
         <v>507</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>508</v>
@@ -11728,7 +11761,7 @@
         <v>73</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="129">
@@ -11739,7 +11772,7 @@
         <v>507</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>512</v>
@@ -11753,36 +11786,36 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>558</v>
+        <v>592</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>560</v>
+        <v>593</v>
       </c>
       <c r="C130" s="1">
         <v>1.0</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>562</v>
+        <v>594</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>567</v>
+        <v>604</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="C131" s="1">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>517</v>
@@ -11889,7 +11922,7 @@
         <v>535</v>
       </c>
       <c r="C136" s="1">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>517</v>
@@ -11898,18 +11931,18 @@
         <v>536</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C137" s="1">
         <v>5.0</v>
@@ -11918,10 +11951,10 @@
         <v>517</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>17</v>
@@ -11929,10 +11962,10 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>545</v>
+        <v>629</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C138" s="1">
         <v>5.0</v>
@@ -11941,10 +11974,10 @@
         <v>517</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>12</v>
@@ -11952,10 +11985,10 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C139" s="1">
         <v>6.0</v>
@@ -11964,21 +11997,21 @@
         <v>517</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C140" s="1">
         <v>3.0</v>
@@ -11987,10 +12020,10 @@
         <v>517</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>27</v>
@@ -11998,10 +12031,10 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C141" s="1">
         <v>2.0</v>
@@ -12010,21 +12043,21 @@
         <v>517</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C142" s="1">
         <v>1.0</v>
@@ -12033,10 +12066,10 @@
         <v>517</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>17</v>
@@ -12044,22 +12077,22 @@
     </row>
     <row r="143">
       <c r="A143" s="3" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C143" s="1">
         <v>1.0</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>17</v>
@@ -12068,22 +12101,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C144" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D144" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E144" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="E144" s="2" t="s">
-        <v>576</v>
-      </c>
       <c r="F144" s="1" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>49</v>
@@ -12091,19 +12124,19 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>32</v>
@@ -12111,22 +12144,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C146" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>49</v>
@@ -12134,22 +12167,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C147" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>27</v>
@@ -12157,19 +12190,19 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>22</v>
@@ -12177,19 +12210,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>594</v>
+        <v>590</v>
+      </c>
+      <c r="C149" s="1">
+        <v>1.0</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E149" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="F149" s="1" t="s">
         <v>595</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>596</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>12</v>
@@ -12197,68 +12233,62 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="C150" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>643</v>
+        <v>670</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>652</v>
+        <v>680</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>653</v>
+        <v>681</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>654</v>
-      </c>
-      <c r="C151" s="1">
-        <v>1.0</v>
+        <v>682</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>655</v>
+        <v>683</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>663</v>
+        <v>691</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>665</v>
+        <v>692</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>666</v>
-      </c>
-      <c r="C152" s="1">
-        <v>1.0</v>
+        <v>693</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>667</v>
+        <v>694</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>673</v>
+        <v>702</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>32</v>
@@ -12266,22 +12296,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B153" s="8" t="s">
         <v>597</v>
-      </c>
-      <c r="B153" s="8" t="s">
-        <v>598</v>
       </c>
       <c r="C153" s="1">
         <v>3.0</v>
       </c>
       <c r="D153" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E153" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="E153" s="1" t="s">
+      <c r="F153" s="1" t="s">
         <v>600</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>601</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>17</v>
@@ -12289,19 +12319,19 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B154" s="7" t="s">
         <v>602</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>603</v>
       </c>
       <c r="C154" s="1">
         <v>2.0</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>605</v>
@@ -12318,10 +12348,10 @@
         <v>607</v>
       </c>
       <c r="C155" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>608</v>
@@ -12341,7 +12371,7 @@
         <v>611</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>612</v>
@@ -12364,7 +12394,7 @@
         <v>1.0</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>616</v>
@@ -12384,7 +12414,7 @@
         <v>619</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E158" s="5" t="s">
         <v>620</v>
@@ -12404,7 +12434,7 @@
         <v>623</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>624</v>
@@ -12413,7 +12443,7 @@
         <v>625</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H159" s="3"/>
     </row>
@@ -12428,13 +12458,13 @@
         <v>1.0</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>628</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>32</v>
@@ -12446,445 +12476,442 @@
         <v>498</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>711</v>
-      </c>
-      <c r="C161" s="1">
-        <v>1.0</v>
+        <v>731</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C162" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>729</v>
+        <v>745</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="s">
-        <v>630</v>
+      <c r="A163" s="6" t="s">
+        <v>569</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>631</v>
+        <v>747</v>
       </c>
       <c r="C163" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>633</v>
+        <v>598</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>749</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>634</v>
+        <v>755</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="C164" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F164" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="B164" s="7" t="s">
-        <v>636</v>
-      </c>
-      <c r="C164" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>638</v>
-      </c>
       <c r="G164" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B165" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="C165" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="F165" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="C165" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="G165" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C166" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="F167" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="D166" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="E166" s="2" t="s">
+      <c r="G167" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="F166" s="1" t="s">
+      <c r="B168" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="G166" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="s">
+      <c r="C168" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E168" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="F168" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="C167" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="G167" s="1" t="s">
+      <c r="G168" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H167" s="3"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="C168" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="G168" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="H168" s="3"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
-        <v>661</v>
+        <v>498</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="C169" s="1">
         <v>3.0</v>
       </c>
       <c r="D169" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C170" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="F170" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="E169" s="2" t="s">
+      <c r="G170" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C171" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H171" s="6"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="F169" s="1" t="s">
+      <c r="C172" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="G169" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="6" t="s">
-        <v>669</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="C170" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H170" s="6"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="C171" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="G171" s="1" t="s">
+      <c r="G172" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C172" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H172" s="3"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="C173" s="1">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>684</v>
+        <v>660</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>672</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="H173" s="3"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="C174" s="11">
-        <v>5.0</v>
-      </c>
-      <c r="D174" s="10" t="s">
-        <v>670</v>
-      </c>
-      <c r="E174" s="1" t="s">
-        <v>688</v>
+        <v>675</v>
+      </c>
+      <c r="C174" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>676</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="H174" s="3"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>691</v>
+        <v>679</v>
+      </c>
+      <c r="C175" s="11">
+        <v>5.0</v>
       </c>
       <c r="D175" s="10" t="s">
-        <v>670</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>692</v>
+        <v>660</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>684</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="H175" s="3"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="B176" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="D176" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H176" s="3"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="D176" s="10" t="s">
-        <v>670</v>
-      </c>
-      <c r="E176" s="2" t="s">
+      <c r="D177" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="E177" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="F176" s="1" t="s">
+      <c r="F177" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="G176" s="1" t="s">
+      <c r="G177" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H176" s="3"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="D177" s="10" t="s">
-        <v>670</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="H177" s="3"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="D178" s="10" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="D179" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="F179" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="D179" s="10" t="s">
-        <v>670</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>706</v>
-      </c>
       <c r="G179" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="s">
-        <v>806</v>
+        <v>704</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="C180" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D180" s="12" t="s">
-        <v>670</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>811</v>
+        <v>705</v>
+      </c>
+      <c r="D180" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>706</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>817</v>
+        <v>707</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>49</v>
@@ -12898,330 +12925,332 @@
         <v>819</v>
       </c>
       <c r="C181" s="1">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D181" s="12" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E181" s="5" t="s">
         <v>820</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C182" s="1">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="D182" s="12" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="s">
-        <v>707</v>
+      <c r="A183" s="1" t="s">
+        <v>838</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>708</v>
+        <v>839</v>
       </c>
       <c r="C183" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>710</v>
+        <v>1.0</v>
+      </c>
+      <c r="D183" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>840</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>713</v>
+        <v>846</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H183" s="3"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C184" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H184" s="3"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C185" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="C184" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="E184" s="2" t="s">
+      <c r="F185" s="1" t="s">
         <v>716</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H184" s="3"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C185" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>724</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="H185" s="3"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>305</v>
+        <v>718</v>
       </c>
       <c r="C186" s="1">
         <v>3.0</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="G186" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C187" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="G187" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="C187" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H187" s="3"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="C188" s="1">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="H188" s="3"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>738</v>
+        <v>729</v>
+      </c>
+      <c r="C189" s="1">
+        <v>5.0</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="H189" s="3"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H190" s="3"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="B191" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="C190" s="1">
+      <c r="C191" s="1">
         <v>5.0</v>
       </c>
-      <c r="D190" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="E190" s="2" t="s">
+      <c r="D191" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E191" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="F190" s="1" t="s">
+      <c r="F191" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="G190" s="1" t="s">
+      <c r="G191" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H190" s="3"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="6" t="s">
-        <v>745</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H191" s="6"/>
+      <c r="H191" s="3"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>749</v>
-      </c>
       <c r="D192" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>750</v>
+        <v>710</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>880</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>73</v>
       </c>
       <c r="G192" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H192" s="6"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G193" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H192" s="6"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C193" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H193" s="3"/>
+      <c r="H193" s="6"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="s">
-        <v>264</v>
+        <v>50</v>
       </c>
       <c r="B194" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C194" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="C194" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>751</v>
-      </c>
       <c r="E194" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H194" s="3"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="s">
-        <v>757</v>
+        <v>264</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>758</v>
       </c>
+      <c r="C195" s="1">
+        <v>6.0</v>
+      </c>
       <c r="D195" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>759</v>
@@ -13235,17 +13264,14 @@
       <c r="H195" s="3"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="s">
+      <c r="A196" s="3" t="s">
         <v>761</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="C196" s="1">
-        <v>5.0</v>
-      </c>
       <c r="D196" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>763</v>
@@ -13254,8 +13280,9 @@
         <v>764</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="H196" s="3"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="s">
@@ -13265,10 +13292,10 @@
         <v>766</v>
       </c>
       <c r="C197" s="1">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>767</v>
@@ -13277,7 +13304,7 @@
         <v>768</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="198">
@@ -13287,8 +13314,11 @@
       <c r="B198" s="1" t="s">
         <v>770</v>
       </c>
+      <c r="C198" s="1">
+        <v>2.0</v>
+      </c>
       <c r="D198" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>771</v>
@@ -13297,7 +13327,7 @@
         <v>772</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="199">
@@ -13308,7 +13338,7 @@
         <v>774</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>775</v>
@@ -13317,67 +13347,64 @@
         <v>776</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="s">
-        <v>889</v>
+        <v>777</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="C200" s="1">
-        <v>1.0</v>
+        <v>778</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>891</v>
+        <v>779</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>895</v>
+        <v>780</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="s">
-        <v>264</v>
+        <v>904</v>
       </c>
       <c r="B201" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="C201" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="C201" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>777</v>
-      </c>
       <c r="E201" s="2" t="s">
-        <v>778</v>
+        <v>906</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>779</v>
+        <v>916</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="s">
-        <v>780</v>
+        <v>264</v>
       </c>
       <c r="B202" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C202" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>781</v>
-      </c>
-      <c r="C202" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>777</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>782</v>
@@ -13386,7 +13413,7 @@
         <v>783</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="203">
@@ -13397,10 +13424,10 @@
         <v>785</v>
       </c>
       <c r="C203" s="1">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>786</v>
@@ -13409,7 +13436,7 @@
         <v>787</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="204">
@@ -13419,8 +13446,11 @@
       <c r="B204" s="1" t="s">
         <v>789</v>
       </c>
+      <c r="C204" s="1">
+        <v>15.0</v>
+      </c>
       <c r="D204" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>790</v>
@@ -13439,11 +13469,8 @@
       <c r="B205" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="C205" s="1">
-        <v>3.0</v>
-      </c>
       <c r="D205" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>794</v>
@@ -13452,7 +13479,7 @@
         <v>795</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="206">
@@ -13462,8 +13489,11 @@
       <c r="B206" s="1" t="s">
         <v>797</v>
       </c>
+      <c r="C206" s="1">
+        <v>3.0</v>
+      </c>
       <c r="D206" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>798</v>
@@ -13472,7 +13502,7 @@
         <v>799</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="207">
@@ -13480,189 +13510,186 @@
         <v>800</v>
       </c>
       <c r="B207" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D207" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="G207" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>804</v>
-      </c>
       <c r="D208" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>805</v>
       </c>
       <c r="F208" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="G208" s="1" t="s">
+      <c r="D209" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="F209" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="G209" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H208" s="3"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="G209" s="1" t="s">
-        <v>135</v>
-      </c>
+      <c r="H209" s="3"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="F210" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>821</v>
-      </c>
       <c r="G210" s="1" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="C213" s="1">
-        <v>4.0</v>
+        <v>827</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>836</v>
+        <v>781</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>840</v>
+        <v>297</v>
       </c>
       <c r="C214" s="1">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D214" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="E214" s="2" t="s">
+      <c r="F214" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="F214" s="1" t="s">
-        <v>842</v>
-      </c>
       <c r="G214" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="B215" s="1" t="s">
+      <c r="C215" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="C215" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="E215" s="2" t="s">
+      <c r="F215" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="F215" s="1" t="s">
-        <v>846</v>
-      </c>
       <c r="G215" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="216">
@@ -13673,19 +13700,19 @@
         <v>848</v>
       </c>
       <c r="C216" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="E216" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>849</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>850</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="217">
@@ -13699,36 +13726,36 @@
         <v>1.0</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="E217" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="E217" s="1" t="s">
         <v>853</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>854</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="s">
-        <v>967</v>
+        <v>855</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>968</v>
+        <v>856</v>
       </c>
       <c r="C218" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="E218" s="5" t="s">
-        <v>969</v>
+        <v>835</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>857</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>970</v>
+        <v>858</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>17</v>
@@ -13742,12 +13769,12 @@
         <v>972</v>
       </c>
       <c r="C219" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="E219" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="E219" s="5" t="s">
         <v>973</v>
       </c>
       <c r="F219" s="1" t="s">
@@ -13768,39 +13795,39 @@
         <v>1.0</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>836</v>
-      </c>
-      <c r="E220" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>977</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>978</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="s">
-        <v>855</v>
+        <v>979</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>95</v>
+        <v>980</v>
       </c>
       <c r="C221" s="1">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>857</v>
+        <v>835</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>981</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>858</v>
+        <v>982</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="222">
@@ -13808,13 +13835,13 @@
         <v>859</v>
       </c>
       <c r="B222" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C222" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>860</v>
-      </c>
-      <c r="C222" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>856</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>861</v>
@@ -13823,7 +13850,7 @@
         <v>862</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="223">
@@ -13833,31 +13860,31 @@
       <c r="B223" s="1" t="s">
         <v>864</v>
       </c>
+      <c r="C223" s="1">
+        <v>4.0</v>
+      </c>
       <c r="D223" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E223" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="F223" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="F223" s="1" t="s">
-        <v>867</v>
-      </c>
       <c r="G223" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="s">
-        <v>223</v>
+        <v>867</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="C224" s="1">
-        <v>1.0</v>
-      </c>
       <c r="D224" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>869</v>
@@ -13866,90 +13893,84 @@
         <v>870</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="B225" s="13" t="s">
+      <c r="C225" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="E225" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="C225" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="E225" s="2" t="s">
+      <c r="F225" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="F225" s="1" t="s">
-        <v>874</v>
-      </c>
       <c r="G225" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="s">
-        <v>395</v>
+        <v>874</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>979</v>
-      </c>
-      <c r="C226" s="1">
-        <v>1.0</v>
+        <v>875</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="E226" s="5" t="s">
-        <v>980</v>
+        <v>860</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>876</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>981</v>
+        <v>877</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C227" s="1">
-        <v>23.0</v>
+        <v>395</v>
+      </c>
+      <c r="B227" s="13" t="s">
+        <v>983</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>877</v>
+        <v>860</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>984</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>878</v>
+        <v>985</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C228" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D228" s="1" t="s">
         <v>879</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="C228" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>876</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>881</v>
@@ -13958,7 +13979,7 @@
         <v>882</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="229">
@@ -13969,10 +13990,10 @@
         <v>884</v>
       </c>
       <c r="C229" s="1">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>885</v>
@@ -13989,134 +14010,137 @@
         <v>887</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C230" s="1">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="C231" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="F231" s="1" t="s">
         <v>893</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>893</v>
-      </c>
-      <c r="C231" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="F231" s="1" t="s">
-        <v>896</v>
-      </c>
       <c r="G231" s="1" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="C232" s="1">
         <v>2.0</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="C233" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="C234" s="1">
         <v>1.0</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="E234" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="F234" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="F234" s="1" t="s">
-        <v>908</v>
-      </c>
       <c r="G234" s="1" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="C235" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="E235" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="E235" s="2" t="s">
+      <c r="F235" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="F235" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="G235" s="1" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
     </row>
     <row r="236">
@@ -14124,13 +14148,13 @@
         <v>912</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>73</v>
@@ -14141,25 +14165,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="C237" s="1">
-        <v>1.0</v>
+        <v>913</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="E237" s="1" t="s">
-        <v>916</v>
+        <v>879</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>917</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>917</v>
+        <v>73</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="238">
@@ -14173,9 +14194,9 @@
         <v>1.0</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="E238" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="E238" s="1" t="s">
         <v>920</v>
       </c>
       <c r="F238" s="1" t="s">
@@ -14192,8 +14213,11 @@
       <c r="B239" s="1" t="s">
         <v>923</v>
       </c>
+      <c r="C239" s="1">
+        <v>1.0</v>
+      </c>
       <c r="D239" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>924</v>
@@ -14202,24 +14226,27 @@
         <v>925</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="s">
-        <v>926</v>
+        <v>986</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>927</v>
+        <v>987</v>
+      </c>
+      <c r="C240" s="1">
+        <v>1.0</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>928</v>
+        <v>988</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>929</v>
+        <v>989</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>27</v>
@@ -14227,222 +14254,262 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>939</v>
-      </c>
-      <c r="C243" s="1">
-        <v>7.0</v>
+        <v>935</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>940</v>
+        <v>879</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C244" s="1">
-        <v>4.0</v>
+        <v>939</v>
       </c>
       <c r="D244" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="E244" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="E244" s="2" t="s">
-        <v>944</v>
-      </c>
       <c r="F244" s="1" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="C245" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="F245" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="C245" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="F245" s="1" t="s">
-        <v>949</v>
-      </c>
       <c r="G245" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>868</v>
+        <v>256</v>
       </c>
       <c r="C246" s="1">
         <v>4.0</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>228</v>
+        <v>951</v>
       </c>
       <c r="C247" s="1">
         <v>2.0</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="s">
-        <v>288</v>
+        <v>954</v>
       </c>
       <c r="B248" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="C248" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="F248" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="C248" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>957</v>
-      </c>
-      <c r="F248" s="1" t="s">
-        <v>958</v>
-      </c>
       <c r="G248" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C249" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="F249" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>960</v>
-      </c>
-      <c r="C249" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="F249" s="1" t="s">
-        <v>962</v>
-      </c>
       <c r="G249" s="1" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="C250" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="G250" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="B250" s="1" t="s">
+      <c r="B251" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="D250" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="E250" s="2" t="s">
+      <c r="C251" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E251" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="F250" s="1" t="s">
+      <c r="F251" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="G250" s="1" t="s">
+      <c r="G251" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="G252" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14612,12 +14679,12 @@
     <hyperlink r:id="rId162" ref="E169"/>
     <hyperlink r:id="rId163" ref="E170"/>
     <hyperlink r:id="rId164" ref="E171"/>
-    <hyperlink r:id="rId165" ref="E173"/>
-    <hyperlink r:id="rId166" ref="E175"/>
+    <hyperlink r:id="rId165" ref="E172"/>
+    <hyperlink r:id="rId166" ref="E174"/>
     <hyperlink r:id="rId167" ref="E176"/>
     <hyperlink r:id="rId168" ref="E177"/>
     <hyperlink r:id="rId169" ref="E178"/>
-    <hyperlink r:id="rId170" ref="E180"/>
+    <hyperlink r:id="rId170" ref="E179"/>
     <hyperlink r:id="rId171" ref="E181"/>
     <hyperlink r:id="rId172" ref="E182"/>
     <hyperlink r:id="rId173" ref="E183"/>
@@ -14629,7 +14696,7 @@
     <hyperlink r:id="rId179" ref="E189"/>
     <hyperlink r:id="rId180" ref="E190"/>
     <hyperlink r:id="rId181" ref="E191"/>
-    <hyperlink r:id="rId182" ref="E193"/>
+    <hyperlink r:id="rId182" ref="E192"/>
     <hyperlink r:id="rId183" ref="E194"/>
     <hyperlink r:id="rId184" ref="E195"/>
     <hyperlink r:id="rId185" ref="E196"/>
@@ -14652,7 +14719,7 @@
     <hyperlink r:id="rId202" ref="E213"/>
     <hyperlink r:id="rId203" ref="E214"/>
     <hyperlink r:id="rId204" ref="E215"/>
-    <hyperlink r:id="rId205" ref="E217"/>
+    <hyperlink r:id="rId205" ref="E216"/>
     <hyperlink r:id="rId206" ref="E218"/>
     <hyperlink r:id="rId207" ref="E219"/>
     <hyperlink r:id="rId208" ref="E220"/>
@@ -14669,9 +14736,9 @@
     <hyperlink r:id="rId219" ref="E231"/>
     <hyperlink r:id="rId220" ref="E232"/>
     <hyperlink r:id="rId221" ref="E233"/>
-    <hyperlink r:id="rId222" ref="E235"/>
+    <hyperlink r:id="rId222" ref="E234"/>
     <hyperlink r:id="rId223" ref="E236"/>
-    <hyperlink r:id="rId224" ref="E238"/>
+    <hyperlink r:id="rId224" ref="E237"/>
     <hyperlink r:id="rId225" ref="E239"/>
     <hyperlink r:id="rId226" ref="E240"/>
     <hyperlink r:id="rId227" ref="E241"/>
@@ -14684,7 +14751,9 @@
     <hyperlink r:id="rId234" ref="E248"/>
     <hyperlink r:id="rId235" ref="E249"/>
     <hyperlink r:id="rId236" ref="E250"/>
+    <hyperlink r:id="rId237" ref="E251"/>
+    <hyperlink r:id="rId238" ref="E252"/>
   </hyperlinks>
-  <drawing r:id="rId237"/>
+  <drawing r:id="rId239"/>
 </worksheet>
 </file>
--- a/PresetGroups.xlsx
+++ b/PresetGroups.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2894" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="987">
   <si>
     <t>NAME</t>
   </si>
@@ -113,39 +113,39 @@
     <t>Renew</t>
   </si>
   <si>
+    <t>Reformist Movement</t>
+  </si>
+  <si>
+    <t>MR</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Mouvement_réformateur_2023.svg/330px-Mouvement_réformateur_2023.svg.png</t>
+  </si>
+  <si>
+    <t>#002BFF</t>
+  </si>
+  <si>
+    <t>Vlaams Belang</t>
+  </si>
+  <si>
+    <t>VB</t>
+  </si>
+  <si>
     <t>Communist Party of Austria</t>
   </si>
   <si>
-    <t>Reformist Movement</t>
-  </si>
-  <si>
     <t>KPÖ</t>
   </si>
   <si>
-    <t>MR</t>
-  </si>
-  <si>
-    <t>Belgium</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Mouvement_réformateur_2023.svg/330px-Mouvement_réformateur_2023.svg.png</t>
+    <t>https://i.ibb.co/Y7jTyQPn/VB.png</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6a/Kommunistische_Partei_%C3%96sterreichs_Logo.svg/1920px-Kommunistische_Partei_%C3%96sterreichs_Logo.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>#002BFF</t>
-  </si>
-  <si>
-    <t>Vlaams Belang</t>
-  </si>
-  <si>
-    <t>VB</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/Y7jTyQPn/VB.png</t>
-  </si>
-  <si>
     <t>#ffe500</t>
   </si>
   <si>
@@ -176,9 +176,15 @@
     <t>#FF0000</t>
   </si>
   <si>
+    <t>#AB0000</t>
+  </si>
+  <si>
     <t>Christian Democratic and Flemish</t>
   </si>
   <si>
+    <t>Left</t>
+  </si>
+  <si>
     <t>CD&amp;V</t>
   </si>
   <si>
@@ -194,12 +200,6 @@
     <t>https://i.ibb.co/ym0RdDdw/Vooruit-logo.png</t>
   </si>
   <si>
-    <t>#AB0000</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
     <t>#FF2900</t>
   </si>
   <si>
@@ -350,6 +350,12 @@
     <t>https://i.ibb.co/dsWxkKd9/logo-white.png</t>
   </si>
   <si>
+    <t>#204A41</t>
+  </si>
+  <si>
+    <t>Non-Inscrits</t>
+  </si>
+  <si>
     <t>#0014FF</t>
   </si>
   <si>
@@ -362,12 +368,6 @@
     <t>https://i.ibb.co/Vcw3SWFK/image.png</t>
   </si>
   <si>
-    <t>#204A41</t>
-  </si>
-  <si>
-    <t>Non-Inscrits</t>
-  </si>
-  <si>
     <t>#034a80</t>
   </si>
   <si>
@@ -569,12 +569,12 @@
     <t>TOP 09</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Logo_of_the_TOP_09_%282021%29.svg/330px-Logo_of_the_TOP_09_%282021%29.svg.png</t>
+  </si>
+  <si>
     <t>#E85726</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Logo_of_the_TOP_09_%282021%29.svg/330px-Logo_of_the_TOP_09_%282021%29.svg.png</t>
-  </si>
-  <si>
     <t>#993366</t>
   </si>
   <si>
@@ -956,6 +956,24 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b3/Renaissance_parti_logo.svg/250px-Renaissance_parti_logo.svg.png</t>
   </si>
   <si>
+    <t>#FFD600</t>
+  </si>
+  <si>
+    <t>Bernard Guetta</t>
+  </si>
+  <si>
+    <t>Ind. ~RE</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/1718798798373_20240618_GUETTA_Bernard_FR_004.jpg/250px-1718798798373_20240618_GUETTA_Bernard_FR_004.jpg</t>
+  </si>
+  <si>
+    <t>Grégory Allione</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e0/1718798679783_20240618_ALLIONE_Gregory_FR_009.jpg/250px-1718798679783_20240618_ALLIONE_Gregory_FR_009.jpg</t>
+  </si>
+  <si>
     <t>Conservative People's Party of Estonia</t>
   </si>
   <si>
@@ -965,48 +983,30 @@
     <t>https://upload.wikimedia.org/wikipedia/en/thumb/a/a1/Conservative_People%27s_Party_of_Estonia_logo.svg/960px-Conservative_People%27s_Party_of_Estonia_logo.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;_=20211222000409</t>
   </si>
   <si>
-    <t>#FFD600</t>
-  </si>
-  <si>
-    <t>Bernard Guetta</t>
-  </si>
-  <si>
-    <t>Ind. ~RE</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/1718798798373_20240618_GUETTA_Bernard_FR_004.jpg/250px-1718798798373_20240618_GUETTA_Bernard_FR_004.jpg</t>
-  </si>
-  <si>
-    <t>Grégory Allione</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e0/1718798679783_20240618_ALLIONE_Gregory_FR_009.jpg/250px-1718798679783_20240618_ALLIONE_Gregory_FR_009.jpg</t>
+    <t>Democratic Movement</t>
+  </si>
+  <si>
+    <t>MoDem</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/tTsRPDT5/logo-modem.png</t>
+  </si>
+  <si>
+    <t>#ef5327</t>
+  </si>
+  <si>
+    <t>Horizons</t>
+  </si>
+  <si>
+    <t>HOR</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/Y71snypk/262445354-132423309213459-1540854826003817855-n.png</t>
   </si>
   <si>
     <t>#0163AF</t>
   </si>
   <si>
-    <t>Democratic Movement</t>
-  </si>
-  <si>
-    <t>MoDem</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/tTsRPDT5/logo-modem.png</t>
-  </si>
-  <si>
-    <t>#ef5327</t>
-  </si>
-  <si>
-    <t>Horizons</t>
-  </si>
-  <si>
-    <t>HOR</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/Y71snypk/262445354-132423309213459-1540854826003817855-n.png</t>
-  </si>
-  <si>
     <t>#0000BA</t>
   </si>
   <si>
@@ -1460,22 +1460,67 @@
     <t>https://i.ibb.co/SDdCjRSf/Logo-of-the-Our-Homeland-Movement.png</t>
   </si>
   <si>
+    <t>#688D1B</t>
+  </si>
+  <si>
+    <t>Fianna Fáil</t>
+  </si>
+  <si>
+    <t>FF</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/jZDxVkGc/Fianna-F-il-logo-2024.png</t>
+  </si>
+  <si>
+    <t>#66BB66</t>
+  </si>
+  <si>
+    <t>Fine Gael</t>
+  </si>
+  <si>
+    <t>FG</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/7xbprGkD/FG-Logo-white-text-2.png</t>
+  </si>
+  <si>
+    <t>#6699FF</t>
+  </si>
+  <si>
+    <t>Sinn Féin</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/23dn4cnd/path1145.png</t>
+  </si>
+  <si>
+    <t>#00635e</t>
+  </si>
+  <si>
+    <t>Labour Party</t>
+  </si>
+  <si>
+    <t>Labour</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/49/The_logo_of_Labour_Party_in_Ireland_2021.svg/330px-The_logo_of_Labour_Party_in_Ireland_2021.svg.png</t>
+  </si>
+  <si>
+    <t>#EB0000</t>
+  </si>
+  <si>
+    <t>Independent Ireland</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
     <t>Panhellenic Socialist Movement  – Movement for Change</t>
   </si>
   <si>
-    <t>#688D1B</t>
-  </si>
-  <si>
-    <t>Fianna Fáil</t>
-  </si>
-  <si>
-    <t>FF</t>
-  </si>
-  <si>
-    <t>Ireland</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/jZDxVkGc/Fianna-F-il-logo-2024.png</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Logo_of_the_Independent_Ireland.png</t>
   </si>
   <si>
     <t>Greek Left Coalition</t>
@@ -1484,51 +1529,6 @@
     <t>ELAS</t>
   </si>
   <si>
-    <t>#66BB66</t>
-  </si>
-  <si>
-    <t>Fine Gael</t>
-  </si>
-  <si>
-    <t>FG</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/7xbprGkD/FG-Logo-white-text-2.png</t>
-  </si>
-  <si>
-    <t>#6699FF</t>
-  </si>
-  <si>
-    <t>Sinn Féin</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/23dn4cnd/path1145.png</t>
-  </si>
-  <si>
-    <t>#00635e</t>
-  </si>
-  <si>
-    <t>Labour Party</t>
-  </si>
-  <si>
-    <t>Labour</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/49/The_logo_of_Labour_Party_in_Ireland_2021.svg/330px-The_logo_of_Labour_Party_in_Ireland_2021.svg.png</t>
-  </si>
-  <si>
-    <t>#EB0000</t>
-  </si>
-  <si>
-    <t>Independent Ireland</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/6/60/Logo_of_the_Independent_Ireland.png</t>
-  </si>
-  <si>
     <t>#3BEE56</t>
   </si>
   <si>
@@ -1544,87 +1544,87 @@
     <t>Michael McNamara</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/1718895518772_20240620_MC_NAMARA_Micheal_IE_004.jpg/250px-1718895518772_20240620_MC_NAMARA_Micheal_IE_004.jpg</t>
+  </si>
+  <si>
+    <t>Brothers of Italy</t>
+  </si>
+  <si>
+    <t>FdI</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/bjdvL3sm/4.png</t>
+  </si>
+  <si>
+    <t>#03386A</t>
+  </si>
+  <si>
+    <t>PD</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/Zpfs54qR/8.png</t>
+  </si>
+  <si>
+    <t>#EF1C27</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Az</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/mCVtTDRK/643418300-1229717076013923-315037651552542281-n.png</t>
+  </si>
+  <si>
+    <t>#2A3271</t>
+  </si>
+  <si>
+    <t>Solidary Democracy</t>
+  </si>
+  <si>
+    <t>DemoS</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/FLMmxZm5/cropped-favicon-demos.png</t>
+  </si>
+  <si>
     <t>Hope for Democracy – Maria Karystianou, Independent Citizens’ Movement</t>
   </si>
   <si>
     <t>ELPIDA</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/1718895518772_20240620_MC_NAMARA_Micheal_IE_004.jpg/250px-1718895518772_20240620_MC_NAMARA_Micheal_IE_004.jpg</t>
+    <t>#467D83</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/en/d/d6/Hope_for_Democracy.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>Brothers of Italy</t>
-  </si>
-  <si>
-    <t>FdI</t>
+    <t>Public Space</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/cKZh9CHk/732813339-122118025497353635-7465241932009101087-n.png</t>
+  </si>
+  <si>
+    <t>#FC4700</t>
+  </si>
+  <si>
+    <t>Five Star Movement</t>
+  </si>
+  <si>
+    <t>M5S</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/4nh8PxGx/13.png</t>
   </si>
   <si>
     <t>#E1B959</t>
   </si>
   <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/bjdvL3sm/4.png</t>
-  </si>
-  <si>
-    <t>#03386A</t>
-  </si>
-  <si>
-    <t>PD</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/Zpfs54qR/8.png</t>
-  </si>
-  <si>
-    <t>#EF1C27</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Az</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/mCVtTDRK/643418300-1229717076013923-315037651552542281-n.png</t>
-  </si>
-  <si>
-    <t>#2A3271</t>
-  </si>
-  <si>
-    <t>Solidary Democracy</t>
-  </si>
-  <si>
-    <t>DemoS</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/FLMmxZm5/cropped-favicon-demos.png</t>
-  </si>
-  <si>
-    <t>#467D83</t>
-  </si>
-  <si>
-    <t>Public Space</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/cKZh9CHk/732813339-122118025497353635-7465241932009101087-n.png</t>
-  </si>
-  <si>
-    <t>#FC4700</t>
-  </si>
-  <si>
-    <t>Five Star Movement</t>
-  </si>
-  <si>
-    <t>M5S</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/4nh8PxGx/13.png</t>
-  </si>
-  <si>
     <t>#FFEB3B</t>
   </si>
   <si>
@@ -1694,100 +1694,175 @@
     <t>SVP</t>
   </si>
   <si>
+    <t>https://i.ibb.co/P8n5n4G/29.png</t>
+  </si>
+  <si>
+    <t>#231F20</t>
+  </si>
+  <si>
+    <t>New Unity</t>
+  </si>
+  <si>
+    <t>JV</t>
+  </si>
+  <si>
+    <t>Latvia</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/k21R627H/3.png</t>
+  </si>
+  <si>
+    <t>#73b845</t>
+  </si>
+  <si>
+    <t>National Alliance</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/993s7rSf/15.png</t>
+  </si>
+  <si>
+    <t>#932330</t>
+  </si>
+  <si>
+    <t>For Latvia's Development</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/7d41t6d2/3ilwip-U2-400x400.png</t>
+  </si>
+  <si>
+    <t>#a2a2a2</t>
+  </si>
+  <si>
+    <t>United List</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/21ktVsB2/11.png</t>
+  </si>
+  <si>
+    <t>#ffa800</t>
+  </si>
+  <si>
+    <t>The Progressives</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/prZWzv9c/Platforma-logo.png</t>
+  </si>
+  <si>
+    <t>#F93B1D</t>
+  </si>
+  <si>
+    <t>Social Democratic Party "Harmony"</t>
+  </si>
+  <si>
+    <t>Saskaņa</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/Q3gs8gMM/417406814-897587372373097-6051379660106823097-n.png</t>
+  </si>
+  <si>
     <t>Soc Dems</t>
   </si>
   <si>
-    <t>https://i.ibb.co/P8n5n4G/29.png</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d8/Social_Democrats_%28Ireland%29_logo.svg/960px-Social_Democrats_%28Ireland%29_logo.svg.png</t>
   </si>
   <si>
-    <t>#231F20</t>
-  </si>
-  <si>
-    <t>New Unity</t>
-  </si>
-  <si>
-    <t>JV</t>
-  </si>
-  <si>
-    <t>Latvia</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/k21R627H/3.png</t>
-  </si>
-  <si>
-    <t>#73b845</t>
-  </si>
-  <si>
-    <t>National Alliance</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/993s7rSf/15.png</t>
+    <t>#EA1B23</t>
+  </si>
+  <si>
+    <t>Latvia First</t>
+  </si>
+  <si>
+    <t>LPV</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Latvia_First_1%21_logo.png/250px-Latvia_First_1%21_logo.png</t>
+  </si>
+  <si>
+    <t>#A8343C</t>
+  </si>
+  <si>
+    <t>Homeland Union</t>
+  </si>
+  <si>
+    <t>TS–LKD</t>
   </si>
   <si>
     <t>#752F8B</t>
   </si>
   <si>
-    <t>#932330</t>
-  </si>
-  <si>
-    <t>For Latvia's Development</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/7d41t6d2/3ilwip-U2-400x400.png</t>
-  </si>
-  <si>
-    <t>#a2a2a2</t>
-  </si>
-  <si>
-    <t>United List</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/21ktVsB2/11.png</t>
-  </si>
-  <si>
-    <t>#ffa800</t>
-  </si>
-  <si>
-    <t>The Progressives</t>
-  </si>
-  <si>
-    <t>PRO</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/prZWzv9c/Platforma-logo.png</t>
-  </si>
-  <si>
-    <t>#F93B1D</t>
-  </si>
-  <si>
-    <t>Social Democratic Party "Harmony"</t>
-  </si>
-  <si>
-    <t>Saskaņa</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/Q3gs8gMM/417406814-897587372373097-6051379660106823097-n.png</t>
-  </si>
-  <si>
-    <t>#EA1B23</t>
-  </si>
-  <si>
-    <t>Latvia First</t>
-  </si>
-  <si>
-    <t>LPV</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Latvia_First_1%21_logo.png/250px-Latvia_First_1%21_logo.png</t>
+    <t>Lithuania</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/b/b3/Homeland_Union_–_Lithuanian_Christian_Democrats.svg/330px-Homeland_Union_–_Lithuanian_Christian_Democrats.svg.png</t>
+  </si>
+  <si>
+    <t>#00A59B</t>
+  </si>
+  <si>
+    <t>Social Democratic Party of Lithuania</t>
+  </si>
+  <si>
+    <t>LSDP</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/zV1gWpRC/LSDP-logo.png</t>
+  </si>
+  <si>
+    <t>#E10514</t>
+  </si>
+  <si>
+    <t>Lithuanian Farmers and Greens Union</t>
+  </si>
+  <si>
+    <t>LVŽS</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/D0CJhJN/lvzs-ecr-logo.png</t>
+  </si>
+  <si>
+    <t>#009846</t>
+  </si>
+  <si>
+    <t>Freedom Party</t>
+  </si>
+  <si>
+    <t>LP</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/gbNcwMnG/734756175-1408419071122401-8907830189896880644-n.png</t>
+  </si>
+  <si>
+    <t>#E852CC</t>
+  </si>
+  <si>
+    <t>Union of Democrats "For Lithuania"</t>
+  </si>
+  <si>
+    <t>DSVL</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/SXjzCy4x/Logo-of-the-Democrats-Union-For-Lithuania.png</t>
+  </si>
+  <si>
+    <t>#271CB2</t>
+  </si>
+  <si>
+    <t>Electoral Action of Poles in Lithuania</t>
+  </si>
+  <si>
+    <t>LLRA–KŠS/AWPL–ZCHR</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/LhS6hSdp/logo-pl-awpl-90.png</t>
   </si>
   <si>
     <t>Unity</t>
@@ -1796,102 +1871,27 @@
     <t>Aontú</t>
   </si>
   <si>
+    <t>#781323</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/en/7/77/Aont%C3%BA_logo.png</t>
   </si>
   <si>
-    <t>#A8343C</t>
-  </si>
-  <si>
-    <t>Homeland Union</t>
-  </si>
-  <si>
-    <t>TS–LKD</t>
-  </si>
-  <si>
-    <t>Lithuania</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/thumb/b/b3/Homeland_Union_–_Lithuanian_Christian_Democrats.svg/330px-Homeland_Union_–_Lithuanian_Christian_Democrats.svg.png</t>
-  </si>
-  <si>
-    <t>#00A59B</t>
-  </si>
-  <si>
-    <t>Social Democratic Party of Lithuania</t>
-  </si>
-  <si>
-    <t>LSDP</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/zV1gWpRC/LSDP-logo.png</t>
+    <t>People and Justice Union</t>
+  </si>
+  <si>
+    <t>TTS</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/1/11/Logo_of_the_People_and_Justice_Union.svg/250px-Logo_of_the_People_and_Justice_Union.svg.png</t>
+  </si>
+  <si>
+    <t>#013861</t>
   </si>
   <si>
     <t>#44532A</t>
   </si>
   <si>
-    <t>#E10514</t>
-  </si>
-  <si>
-    <t>Lithuanian Farmers and Greens Union</t>
-  </si>
-  <si>
-    <t>LVŽS</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/D0CJhJN/lvzs-ecr-logo.png</t>
-  </si>
-  <si>
-    <t>#009846</t>
-  </si>
-  <si>
-    <t>Freedom Party</t>
-  </si>
-  <si>
-    <t>LP</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/gbNcwMnG/734756175-1408419071122401-8907830189896880644-n.png</t>
-  </si>
-  <si>
-    <t>#E852CC</t>
-  </si>
-  <si>
-    <t>Union of Democrats "For Lithuania"</t>
-  </si>
-  <si>
-    <t>DSVL</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/SXjzCy4x/Logo-of-the-Democrats-Union-For-Lithuania.png</t>
-  </si>
-  <si>
-    <t>#271CB2</t>
-  </si>
-  <si>
-    <t>Electoral Action of Poles in Lithuania</t>
-  </si>
-  <si>
-    <t>LLRA–KŠS/AWPL–ZCHR</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/LhS6hSdp/logo-pl-awpl-90.png</t>
-  </si>
-  <si>
-    <t>#781323</t>
-  </si>
-  <si>
-    <t>People and Justice Union</t>
-  </si>
-  <si>
-    <t>TTS</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/thumb/1/11/Logo_of_the_People_and_Justice_Union.svg/250px-Logo_of_the_People_and_Justice_Union.svg.png</t>
-  </si>
-  <si>
-    <t>#013861</t>
-  </si>
-  <si>
     <t>Liberals' Movement</t>
   </si>
   <si>
@@ -1901,69 +1901,69 @@
     <t>https://i.ibb.co/v4kfT7g1/Untitled-design-7.png</t>
   </si>
   <si>
+    <t>#F29402</t>
+  </si>
+  <si>
+    <t>Christian Social People's Party</t>
+  </si>
+  <si>
+    <t>CSV</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/9/96/Logo_of_the_Christian_Social_People%27s_Party_%282022%29.svg/330px-Logo_of_the_Christian_Social_People%27s_Party_%282022%29.svg.png</t>
+  </si>
+  <si>
+    <t>#FFC300</t>
+  </si>
+  <si>
+    <t>Luxembourg Socialist Workers' Party</t>
+  </si>
+  <si>
+    <t>LSAP</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9e/Logo_of_the_Luxembourg_Socialist_Workers%27_Party.svg/250px-Logo_of_the_Luxembourg_Socialist_Workers%27_Party.svg.png</t>
+  </si>
+  <si>
+    <t>#F00035</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/zT4fTq7S/Demokratesch-Partei.png</t>
+  </si>
+  <si>
+    <t>#002C4F</t>
+  </si>
+  <si>
+    <t>The Greens</t>
+  </si>
+  <si>
+    <t>Gréng</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/BKf4czM7/logo-15.png</t>
+  </si>
+  <si>
+    <t>#8EB74A</t>
+  </si>
+  <si>
+    <t>Alternative Democratic Reform Party</t>
+  </si>
+  <si>
+    <t>ADR</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Logo_of_the_Alternative_Democratic_Reform_Party_%282022%29.svg/330px-Logo_of_the_Alternative_Democratic_Reform_Party_%282022%29.svg.png</t>
+  </si>
+  <si>
     <t>League</t>
   </si>
   <si>
-    <t>#F29402</t>
-  </si>
-  <si>
-    <t>Christian Social People's Party</t>
-  </si>
-  <si>
-    <t>CSV</t>
-  </si>
-  <si>
-    <t>Luxembourg</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/thumb/9/96/Logo_of_the_Christian_Social_People%27s_Party_%282022%29.svg/330px-Logo_of_the_Christian_Social_People%27s_Party_%282022%29.svg.png</t>
-  </si>
-  <si>
-    <t>#FFC300</t>
-  </si>
-  <si>
-    <t>Luxembourg Socialist Workers' Party</t>
-  </si>
-  <si>
-    <t>LSAP</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9e/Logo_of_the_Luxembourg_Socialist_Workers%27_Party.svg/250px-Logo_of_the_Luxembourg_Socialist_Workers%27_Party.svg.png</t>
-  </si>
-  <si>
-    <t>#F00035</t>
-  </si>
-  <si>
-    <t>DP</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/zT4fTq7S/Demokratesch-Partei.png</t>
-  </si>
-  <si>
-    <t>#002C4F</t>
-  </si>
-  <si>
-    <t>The Greens</t>
-  </si>
-  <si>
-    <t>Gréng</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/BKf4czM7/logo-15.png</t>
-  </si>
-  <si>
-    <t>#8EB74A</t>
-  </si>
-  <si>
-    <t>Alternative Democratic Reform Party</t>
-  </si>
-  <si>
-    <t>ADR</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a4/Logo_of_the_Alternative_Democratic_Reform_Party_%282022%29.svg/330px-Logo_of_the_Alternative_Democratic_Reform_Party_%282022%29.svg.png</t>
-  </si>
-  <si>
     <t>#00ADDC</t>
   </si>
   <si>
@@ -2012,79 +2012,151 @@
     <t>https://upload.wikimedia.org/wikipedia/en/thumb/7/76/Party_for_Freedom_logo.svg/330px-Party_for_Freedom_logo.svg.png</t>
   </si>
   <si>
+    <t>#234672</t>
+  </si>
+  <si>
+    <t>People's Party for Freedom and Democracy</t>
+  </si>
+  <si>
+    <t>VVD</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7a/VVD_logo_%282020–present%29.svg/250px-VVD_logo_%282020–present%29.svg.png</t>
+  </si>
+  <si>
+    <t>#0328CB</t>
+  </si>
+  <si>
+    <t>Christian Democratic Appeal</t>
+  </si>
+  <si>
+    <t>CDA</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/CDA_logo_2021.svg/250px-CDA_logo_2021.svg.png</t>
+  </si>
+  <si>
+    <t>#1F9359</t>
+  </si>
+  <si>
+    <t>Democrats 66</t>
+  </si>
+  <si>
+    <t>D66</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e9/D66_logo_%282019–present%29.svg/330px-D66_logo_%282019–present%29.svg.png</t>
+  </si>
+  <si>
+    <t>#00AE41</t>
+  </si>
+  <si>
+    <t>Farmer–Citizen Movement</t>
+  </si>
+  <si>
+    <t>BBB</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/BoerBurgerBeweging_logo.svg/330px-BoerBurgerBeweging_logo.svg.png</t>
+  </si>
+  <si>
+    <t>#95C11F</t>
+  </si>
+  <si>
+    <t>Volt Netherlands</t>
+  </si>
+  <si>
+    <t>Party for the Animals</t>
+  </si>
+  <si>
+    <t>PvdD</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/m53wFmSx/Party-for-the-Animals-logo.png</t>
+  </si>
+  <si>
+    <t>#00743C</t>
+  </si>
+  <si>
+    <t>New Social Contract</t>
+  </si>
+  <si>
+    <t>NSC</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/db/NSC_partijlogo.svg/330px-NSC_partijlogo.svg.png</t>
+  </si>
+  <si>
+    <t>#F0C400</t>
+  </si>
+  <si>
     <t>Sovereign Power</t>
   </si>
   <si>
     <t xml:space="preserve">SV </t>
   </si>
   <si>
-    <t>#234672</t>
-  </si>
-  <si>
-    <t>People's Party for Freedom and Democracy</t>
+    <t>Reformed Political Party</t>
+  </si>
+  <si>
+    <t>SGP</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/80/Suver%C4%93n%C4%81_vara_2024.svg/960px-Suver%C4%93n%C4%81_vara_2024.svg.png</t>
   </si>
   <si>
-    <t>VVD</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7a/VVD_logo_%282020–present%29.svg/250px-VVD_logo_%282020–present%29.svg.png</t>
-  </si>
-  <si>
-    <t>#0328CB</t>
-  </si>
-  <si>
-    <t>Christian Democratic Appeal</t>
-  </si>
-  <si>
-    <t>CDA</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/CDA_logo_2021.svg/250px-CDA_logo_2021.svg.png</t>
-  </si>
-  <si>
-    <t>#1F9359</t>
-  </si>
-  <si>
-    <t>Democrats 66</t>
-  </si>
-  <si>
-    <t>D66</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/SGP_logo_%282016–present%29.svg/330px-SGP_logo_%282016–present%29.svg.png</t>
+  </si>
+  <si>
+    <t>#EA5D06</t>
+  </si>
+  <si>
+    <t>Civic Coalition</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a6/Logo_Koalicja_Obywatelska_2023_serce.svg/330px-Logo_Koalicja_Obywatelska_2023_serce.svg.png</t>
+  </si>
+  <si>
+    <t>#F68F2D</t>
   </si>
   <si>
     <t>#6767AB</t>
   </si>
   <si>
+    <t>Law and Justice</t>
+  </si>
+  <si>
+    <t>PiS</t>
+  </si>
+  <si>
     <t>We Change the Rules</t>
   </si>
   <si>
     <t>MMN</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/2/2a/Logo_of_the_Law_and_Justice.svg/250px-Logo_of_the_Law_and_Justice.svg.png</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Latvia_road_sign_330.svg/960px-Latvia_road_sign_330.svg.png</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e9/D66_logo_%282019–present%29.svg/330px-D66_logo_%282019–present%29.svg.png</t>
-  </si>
-  <si>
-    <t>#00AE41</t>
-  </si>
-  <si>
-    <t>Farmer–Citizen Movement</t>
-  </si>
-  <si>
-    <t>BBB</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/BoerBurgerBeweging_logo.svg/330px-BoerBurgerBeweging_logo.svg.png</t>
-  </si>
-  <si>
-    <t>#95C11F</t>
-  </si>
-  <si>
-    <t>Volt Netherlands</t>
+    <t>#073A76</t>
+  </si>
+  <si>
+    <t>Development Plus</t>
+  </si>
+  <si>
+    <t>R+</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/5hrjXQQD/Rozw-j-Plus.png</t>
   </si>
   <si>
     <t>#19191E</t>
@@ -2099,102 +2171,30 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b1/Za%C4%BCo_un_Zemnieku_savien%C4%ABba_Logo.svg/1920px-Za%C4%BCo_un_Zemnieku_savien%C4%ABba_Logo.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Party for the Animals</t>
-  </si>
-  <si>
-    <t>PvdD</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/m53wFmSx/Party-for-the-Animals-logo.png</t>
-  </si>
-  <si>
-    <t>#00743C</t>
-  </si>
-  <si>
-    <t>New Social Contract</t>
-  </si>
-  <si>
-    <t>NSC</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/db/NSC_partijlogo.svg/330px-NSC_partijlogo.svg.png</t>
+    <t>#75BAFF</t>
+  </si>
+  <si>
+    <t>National Movement</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/zTYWnbx2/National-Movement-Poland-logo.png</t>
+  </si>
+  <si>
+    <t>#CF1020</t>
+  </si>
+  <si>
+    <t>New Hope</t>
+  </si>
+  <si>
+    <t>NN</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/gMX6N71Q/Nowa-Nadzieja.png</t>
   </si>
   <si>
     <t>#03723A</t>
   </si>
   <si>
-    <t>#F0C400</t>
-  </si>
-  <si>
-    <t>Reformed Political Party</t>
-  </si>
-  <si>
-    <t>SGP</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/SGP_logo_%282016–present%29.svg/330px-SGP_logo_%282016–present%29.svg.png</t>
-  </si>
-  <si>
-    <t>#EA5D06</t>
-  </si>
-  <si>
-    <t>Civic Coalition</t>
-  </si>
-  <si>
-    <t>KO</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a6/Logo_Koalicja_Obywatelska_2023_serce.svg/330px-Logo_Koalicja_Obywatelska_2023_serce.svg.png</t>
-  </si>
-  <si>
-    <t>#F68F2D</t>
-  </si>
-  <si>
-    <t>Law and Justice</t>
-  </si>
-  <si>
-    <t>PiS</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/thumb/2/2a/Logo_of_the_Law_and_Justice.svg/250px-Logo_of_the_Law_and_Justice.svg.png</t>
-  </si>
-  <si>
-    <t>#073A76</t>
-  </si>
-  <si>
-    <t>Development Plus</t>
-  </si>
-  <si>
-    <t>R+</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/5hrjXQQD/Rozw-j-Plus.png</t>
-  </si>
-  <si>
-    <t>#75BAFF</t>
-  </si>
-  <si>
-    <t>National Movement</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/zTYWnbx2/National-Movement-Poland-logo.png</t>
-  </si>
-  <si>
-    <t>#CF1020</t>
-  </si>
-  <si>
-    <t>New Hope</t>
-  </si>
-  <si>
-    <t>NN</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/gMX6N71Q/Nowa-Nadzieja.png</t>
-  </si>
-  <si>
     <t>#E8B909</t>
   </si>
   <si>
@@ -2207,22 +2207,82 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Confederation_of_the_Polish_Crown_logo_%28shield_cropped%29.png</t>
   </si>
   <si>
+    <t>#A37919</t>
+  </si>
+  <si>
+    <t>Polish People's Party</t>
+  </si>
+  <si>
+    <t>PSL</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/Logo_of_the_Polish_People%27s_Party_%282019_color%29_%28four-leaf_clover_cropped%29.svg/250px-Logo_of_the_Polish_People%27s_Party_%282019_color%29_%28four-leaf_clover_cropped%29.svg.png</t>
+  </si>
+  <si>
+    <t>#2ED397</t>
+  </si>
+  <si>
+    <t>New Left</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/20/Lewica_01.svg/330px-Lewica_01.svg.png</t>
+  </si>
+  <si>
+    <t>#AC145A</t>
+  </si>
+  <si>
+    <t>Centre Union</t>
+  </si>
+  <si>
+    <t>UC</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/d/de/Centrum_parliamentary_circle_logo.png</t>
+  </si>
+  <si>
+    <t>Ewa Zajączkowska-Hernik</t>
+  </si>
+  <si>
+    <t>Ind. ex-NN</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/Ewa_Zajączkowska-Hernik_MEP_%282024%29.jpg/250px-Ewa_Zajączkowska-Hernik_MEP_%282024%29.jpg</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/JwFWdv6C/Partido-Socialista-logo.png</t>
+  </si>
+  <si>
     <t xml:space="preserve">DP </t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7f/Darbo_Partija_Logo.svg/1280px-Darbo_Partija_Logo.svg.png</t>
   </si>
   <si>
-    <t>#A37919</t>
-  </si>
-  <si>
-    <t>Polish People's Party</t>
-  </si>
-  <si>
-    <t>PSL</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/Logo_of_the_Polish_People%27s_Party_%282019_color%29_%28four-leaf_clover_cropped%29.svg/250px-Logo_of_the_Polish_People%27s_Party_%282019_color%29_%28four-leaf_clover_cropped%29.svg.png</t>
+    <t>#FF66FF</t>
+  </si>
+  <si>
+    <t>PSD</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/tPMfs461/Partido-Social-Democrata-Logo.png</t>
+  </si>
+  <si>
+    <t>#FF9900</t>
+  </si>
+  <si>
+    <t>CDS – People's Party</t>
+  </si>
+  <si>
+    <t>CDS–PP</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/jPKH7X7p/CDS-People-s-Party-logo.png</t>
   </si>
   <si>
     <t>#1E578C</t>
@@ -2231,117 +2291,57 @@
     <t>Political Party "Dawn of Nemunas"</t>
   </si>
   <si>
+    <t>#0093DD</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/en/thumb/c/c9/Logo_of_the_Dawn_of_Nemunas.svg/960px-Logo_of_the_Dawn_of_Nemunas.svg.png</t>
   </si>
   <si>
-    <t>#2ED397</t>
-  </si>
-  <si>
-    <t>New Left</t>
-  </si>
-  <si>
-    <t>NL</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/20/Lewica_01.svg/330px-Lewica_01.svg.png</t>
-  </si>
-  <si>
-    <t>#AC145A</t>
+    <t>Chega!</t>
+  </si>
+  <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/thumb/9/9d/Logo_of_the_Chega_%28political_party%29.svg/250px-Logo_of_the_Chega_%28political_party%29.svg.png</t>
+  </si>
+  <si>
+    <t>#222256</t>
   </si>
   <si>
     <t>#F25D23</t>
   </si>
   <si>
-    <t>Centre Union</t>
+    <t>Liberal Initiative</t>
+  </si>
+  <si>
+    <t>IL</t>
   </si>
   <si>
     <t>NS</t>
   </si>
   <si>
-    <t>UC</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/NS-logotipas.svg/1280px-NS-logotipas.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/d/de/Centrum_parliamentary_circle_logo.png</t>
-  </si>
-  <si>
-    <t>Ewa Zajączkowska-Hernik</t>
-  </si>
-  <si>
-    <t>Ind. ex-NN</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/Ewa_Zajączkowska-Hernik_MEP_%282024%29.jpg/250px-Ewa_Zajączkowska-Hernik_MEP_%282024%29.jpg</t>
-  </si>
-  <si>
-    <t>Portugal</t>
+    <t>https://i.ibb.co/84Xk0723/Iniciativa-Liberal-logo-1.png</t>
+  </si>
+  <si>
+    <t>#00ADEF</t>
+  </si>
+  <si>
+    <t>Left Bloc</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/N22TY6Gd/Left-Bloc.png</t>
   </si>
   <si>
     <t>#B81E23</t>
   </si>
   <si>
-    <t>https://i.ibb.co/JwFWdv6C/Partido-Socialista-logo.png</t>
-  </si>
-  <si>
-    <t>#FF66FF</t>
-  </si>
-  <si>
-    <t>PSD</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/tPMfs461/Partido-Social-Democrata-Logo.png</t>
-  </si>
-  <si>
-    <t>#FF9900</t>
-  </si>
-  <si>
-    <t>CDS – People's Party</t>
-  </si>
-  <si>
-    <t>CDS–PP</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/jPKH7X7p/CDS-People-s-Party-logo.png</t>
-  </si>
-  <si>
-    <t>#0093DD</t>
-  </si>
-  <si>
-    <t>Chega!</t>
-  </si>
-  <si>
-    <t>CH</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/thumb/9/9d/Logo_of_the_Chega_%28political_party%29.svg/250px-Logo_of_the_Chega_%28political_party%29.svg.png</t>
-  </si>
-  <si>
-    <t>#222256</t>
-  </si>
-  <si>
-    <t>Liberal Initiative</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/84Xk0723/Iniciativa-Liberal-logo-1.png</t>
-  </si>
-  <si>
-    <t>#00ADEF</t>
-  </si>
-  <si>
-    <t>Left Bloc</t>
-  </si>
-  <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/N22TY6Gd/Left-Bloc.png</t>
-  </si>
-  <si>
     <t>#EE4655</t>
   </si>
   <si>
@@ -2468,66 +2468,126 @@
     <t>https://i.ibb.co/TxTs73X2/Logo-of-the-Romanian-National-Conservative-Party.png</t>
   </si>
   <si>
+    <t>#1665FE</t>
+  </si>
+  <si>
+    <t>Social Liberal Humanist Party</t>
+  </si>
+  <si>
+    <t>PUSL</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/dsMtscf4/Logo-balanta-site-bold-t-1-1.png</t>
+  </si>
+  <si>
+    <t>#1B6AB4</t>
+  </si>
+  <si>
+    <t>Health Education Nature Sustainability Party</t>
+  </si>
+  <si>
+    <t>SENS</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/51/SENS_logo.svg/330px-SENS_logo.svg.png</t>
+  </si>
+  <si>
+    <t>#A2DA5A</t>
+  </si>
+  <si>
+    <t>Progressive Slovakia</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Logo_of_the_Progressive_Slovakia_%282021%29.svg/250px-Logo_of_the_Progressive_Slovakia_%282021%29.svg.png</t>
+  </si>
+  <si>
+    <t>#00BFFF</t>
+  </si>
+  <si>
+    <t>Direction – Social Democracy</t>
+  </si>
+  <si>
+    <t>Smer</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/RGwNfChp/Logo-of-the-Direction-Slovak-Social-Democracy.png</t>
+  </si>
+  <si>
     <t>Right Answer 21</t>
   </si>
   <si>
     <t>JA21</t>
   </si>
   <si>
+    <t>#D82222</t>
+  </si>
+  <si>
+    <t>Republic Movement</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/JA21_logo.svg/960px-JA21_logo.svg.png</t>
   </si>
   <si>
-    <t>#1665FE</t>
-  </si>
-  <si>
-    <t>Social Liberal Humanist Party</t>
-  </si>
-  <si>
-    <t>PUSL</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/dsMtscf4/Logo-balanta-site-bold-t-1-1.png</t>
-  </si>
-  <si>
-    <t>#1B6AB4</t>
-  </si>
-  <si>
-    <t>Health Education Nature Sustainability Party</t>
-  </si>
-  <si>
-    <t>SENS</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/51/SENS_logo.svg/330px-SENS_logo.svg.png</t>
+    <t>REP</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Logo_of_the_Republic_%28Slovakia%29.svg/330px-Logo_of_the_Republic_%28Slovakia%29.svg.png</t>
+  </si>
+  <si>
+    <t>#E30512</t>
   </si>
   <si>
     <t>#1F2756</t>
   </si>
   <si>
+    <t>Voice – Social Democracy</t>
+  </si>
+  <si>
+    <t>Hlas</t>
+  </si>
+  <si>
     <t>Forum for Democracy</t>
   </si>
   <si>
     <t>FvD</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Logo_of_the_Voice_–_Social_Democracy.svg/330px-Logo_of_the_Voice_–_Social_Democracy.svg.png</t>
+  </si>
+  <si>
+    <t>#830F38</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b6/FVD_logo.svg/1920px-FVD_logo.svg.png</t>
   </si>
   <si>
-    <t>#A2DA5A</t>
-  </si>
-  <si>
-    <t>Progressive Slovakia</t>
-  </si>
-  <si>
-    <t>Slovakia</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1e/Logo_of_the_Progressive_Slovakia_%282021%29.svg/250px-Logo_of_the_Progressive_Slovakia_%282021%29.svg.png</t>
+    <t>Christian Democratic Movement</t>
+  </si>
+  <si>
+    <t>KDH</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/KDH_Logo.svg/330px-KDH_Logo.svg.png</t>
+  </si>
+  <si>
+    <t>#173A70</t>
+  </si>
+  <si>
+    <t>Slovenian Democratic Party</t>
   </si>
   <si>
     <t>#A71C20</t>
   </si>
   <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ef/SDS_logotype.svg/330px-SDS_logotype.svg.png</t>
+  </si>
+  <si>
     <t>50Plus</t>
   </si>
   <si>
@@ -2537,81 +2597,21 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ec/50PLUS_%28nl%29_Logo.svg/1280px-50PLUS_%28nl%29_Logo.svg.png</t>
   </si>
   <si>
-    <t>#00BFFF</t>
-  </si>
-  <si>
-    <t>Direction – Social Democracy</t>
-  </si>
-  <si>
-    <t>Smer</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/RGwNfChp/Logo-of-the-Direction-Slovak-Social-Democracy.png</t>
-  </si>
-  <si>
-    <t>#D82222</t>
+    <t>#FCDC00</t>
+  </si>
+  <si>
+    <t>Freedom Movement</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Svoboda-logo_2025.svg/330px-Svoboda-logo_2025.svg.png</t>
   </si>
   <si>
     <t>#92107D</t>
   </si>
   <si>
-    <t>Republic Movement</t>
-  </si>
-  <si>
-    <t>REP</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Logo_of_the_Republic_%28Slovakia%29.svg/330px-Logo_of_the_Republic_%28Slovakia%29.svg.png</t>
-  </si>
-  <si>
-    <t>#E30512</t>
-  </si>
-  <si>
-    <t>Voice – Social Democracy</t>
-  </si>
-  <si>
-    <t>Hlas</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Logo_of_the_Voice_–_Social_Democracy.svg/330px-Logo_of_the_Voice_–_Social_Democracy.svg.png</t>
-  </si>
-  <si>
-    <t>#830F38</t>
-  </si>
-  <si>
-    <t>Christian Democratic Movement</t>
-  </si>
-  <si>
-    <t>KDH</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/34/KDH_Logo.svg/330px-KDH_Logo.svg.png</t>
-  </si>
-  <si>
-    <t>#173A70</t>
-  </si>
-  <si>
-    <t>Slovenian Democratic Party</t>
-  </si>
-  <si>
-    <t>Slovenia</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ef/SDS_logotype.svg/330px-SDS_logotype.svg.png</t>
-  </si>
-  <si>
-    <t>#FCDC00</t>
-  </si>
-  <si>
-    <t>Freedom Movement</t>
-  </si>
-  <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Svoboda-logo_2025.svg/330px-Svoboda-logo_2025.svg.png</t>
-  </si>
-  <si>
     <t>#00569D</t>
   </si>
   <si>
@@ -2654,54 +2654,54 @@
     <t>Spain</t>
   </si>
   <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3c/Logo_del_PP_%282022%29.svg/330px-Logo_del_PP_%282022%29.svg.png</t>
+  </si>
+  <si>
+    <t>#1D84CE</t>
+  </si>
+  <si>
+    <t>Spanish Socialist Workers' Party</t>
+  </si>
+  <si>
+    <t>PSOE</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/hRhRpBsT/logo-psoe.png</t>
+  </si>
+  <si>
+    <t>#FF0A06</t>
+  </si>
+  <si>
+    <t>Socialists' Party of Catalonia</t>
+  </si>
+  <si>
+    <t>PSC</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/32/Logo_PSC_oficial_2021.svg/330px-Logo_PSC_oficial_2021.svg.png</t>
+  </si>
+  <si>
+    <t>#E20A16</t>
+  </si>
+  <si>
+    <t>Vox</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/VOX_logo.svg/330px-VOX_logo.svg.png</t>
+  </si>
+  <si>
+    <t>#5AC035</t>
+  </si>
+  <si>
+    <t>Podemos</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Logo_de_Podemos_%282022%29.svg/330px-Logo_de_Podemos_%282022%29.svg.png</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/23/1718288389061_20240611_KOBOSKO_Michal_PL_004.jpg/250px-1718288389061_20240611_KOBOSKO_Michal_PL_004.jpg</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3c/Logo_del_PP_%282022%29.svg/330px-Logo_del_PP_%282022%29.svg.png</t>
-  </si>
-  <si>
-    <t>#1D84CE</t>
-  </si>
-  <si>
-    <t>Spanish Socialist Workers' Party</t>
-  </si>
-  <si>
-    <t>PSOE</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/hRhRpBsT/logo-psoe.png</t>
-  </si>
-  <si>
-    <t>#FF0A06</t>
-  </si>
-  <si>
-    <t>Socialists' Party of Catalonia</t>
-  </si>
-  <si>
-    <t>PSC</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/32/Logo_PSC_oficial_2021.svg/330px-Logo_PSC_oficial_2021.svg.png</t>
-  </si>
-  <si>
-    <t>#E20A16</t>
-  </si>
-  <si>
-    <t>Vox</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/VOX_logo.svg/330px-VOX_logo.svg.png</t>
-  </si>
-  <si>
-    <t>#5AC035</t>
-  </si>
-  <si>
-    <t>Podemos</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Logo_de_Podemos_%282022%29.svg/330px-Logo_de_Podemos_%282022%29.svg.png</t>
-  </si>
-  <si>
     <t>#9269F5</t>
   </si>
   <si>
@@ -2726,6 +2726,93 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/66/Comuns_Sumar_logo_sin_fondo.svg/250px-Comuns_Sumar_logo_sin_fondo.svg.png</t>
   </si>
   <si>
+    <t>#A6214B</t>
+  </si>
+  <si>
+    <t>Se Acabó La Fiesta</t>
+  </si>
+  <si>
+    <t>SALF</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/c/c4/Logo_of_the_Se_Acabó_La_Fiesta.png</t>
+  </si>
+  <si>
+    <t>#785A46</t>
+  </si>
+  <si>
+    <t>Diego Solier</t>
+  </si>
+  <si>
+    <t>Ind. ex-SALF</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/3YR8ZfTC/1720511557800-20240709-SOLIER-FERNANDEZ-Diego-ES-021.jpg</t>
+  </si>
+  <si>
+    <t>Nora Junco</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/1720511531541_20240709_JUNCO_GARCIA_Nora_ES_011.jpg/250px-1720511531541_20240709_JUNCO_GARCIA_Nora_ES_011.jpg</t>
+  </si>
+  <si>
+    <t>Més–Compromís</t>
+  </si>
+  <si>
+    <t>Més</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/27/Més-Compromís_2021_logo.svg/330px-Més-Compromís_2021_logo.svg.png</t>
+  </si>
+  <si>
+    <t>#F15A34</t>
+  </si>
+  <si>
+    <t>Republican Left of Catalonia</t>
+  </si>
+  <si>
+    <t>ERC</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/2YhXRQHC/ERC-logo-2025.png</t>
+  </si>
+  <si>
+    <t>#F95838</t>
+  </si>
+  <si>
+    <t>EH Bildu</t>
+  </si>
+  <si>
+    <t>EHB</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/95/Icono_de_EH_Bildu_%282023%29.svg/330px-Icono_de_EH_Bildu_%282023%29.svg.png</t>
+  </si>
+  <si>
+    <t>#00C19F</t>
+  </si>
+  <si>
+    <t>Galician Nationalist Bloc</t>
+  </si>
+  <si>
+    <t>BNG</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/k637QxD8/path622.png</t>
+  </si>
+  <si>
+    <t>#76b2e1</t>
+  </si>
+  <si>
+    <t>Together for Catalonia</t>
+  </si>
+  <si>
+    <t>Junts</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a8/Logotip_Junts_per_Catalunya.svg/330px-Logotip_Junts_per_Catalunya.svg.png</t>
+  </si>
+  <si>
     <t>FREE</t>
   </si>
   <si>
@@ -2735,108 +2822,21 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e5/Logo_of_the_LIVRE.svg/960px-Logo_of_the_LIVRE.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>#A6214B</t>
-  </si>
-  <si>
-    <t>Se Acabó La Fiesta</t>
-  </si>
-  <si>
-    <t>SALF</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/c/c4/Logo_of_the_Se_Acabó_La_Fiesta.png</t>
-  </si>
-  <si>
-    <t>#785A46</t>
-  </si>
-  <si>
-    <t>Diego Solier</t>
-  </si>
-  <si>
-    <t>Ind. ex-SALF</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/3YR8ZfTC/1720511557800-20240709-SOLIER-FERNANDEZ-Diego-ES-021.jpg</t>
-  </si>
-  <si>
-    <t>Nora Junco</t>
+    <t>#00C3B2</t>
+  </si>
+  <si>
+    <t>Basque Nationalist Party</t>
+  </si>
+  <si>
+    <t>EAJ-PNV</t>
+  </si>
+  <si>
+    <t>https://i.ibb.co/HLzQtDbn/logotipo-eaj-pnv-2025-300.png</t>
   </si>
   <si>
     <t>#C2D217</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/1720511531541_20240709_JUNCO_GARCIA_Nora_ES_011.jpg/250px-1720511531541_20240709_JUNCO_GARCIA_Nora_ES_011.jpg</t>
-  </si>
-  <si>
-    <t>Més–Compromís</t>
-  </si>
-  <si>
-    <t>Més</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/27/Més-Compromís_2021_logo.svg/330px-Més-Compromís_2021_logo.svg.png</t>
-  </si>
-  <si>
-    <t>#F15A34</t>
-  </si>
-  <si>
-    <t>Republican Left of Catalonia</t>
-  </si>
-  <si>
-    <t>ERC</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/2YhXRQHC/ERC-logo-2025.png</t>
-  </si>
-  <si>
-    <t>#F95838</t>
-  </si>
-  <si>
-    <t>EH Bildu</t>
-  </si>
-  <si>
-    <t>EHB</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/95/Icono_de_EH_Bildu_%282023%29.svg/330px-Icono_de_EH_Bildu_%282023%29.svg.png</t>
-  </si>
-  <si>
-    <t>#00C19F</t>
-  </si>
-  <si>
-    <t>Galician Nationalist Bloc</t>
-  </si>
-  <si>
-    <t>BNG</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/k637QxD8/path622.png</t>
-  </si>
-  <si>
-    <t>#76b2e1</t>
-  </si>
-  <si>
-    <t>Together for Catalonia</t>
-  </si>
-  <si>
-    <t>Junts</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a8/Logotip_Junts_per_Catalunya.svg/330px-Logotip_Junts_per_Catalunya.svg.png</t>
-  </si>
-  <si>
-    <t>#00C3B2</t>
-  </si>
-  <si>
-    <t>Basque Nationalist Party</t>
-  </si>
-  <si>
-    <t>EAJ-PNV</t>
-  </si>
-  <si>
-    <t>https://i.ibb.co/HLzQtDbn/logotipo-eaj-pnv-2025-300.png</t>
-  </si>
-  <si>
     <t>#499E37</t>
   </si>
   <si>
@@ -2973,15 +2973,6 @@
   </si>
   <si>
     <t>Catalonia in Common</t>
-  </si>
-  <si>
-    <t>CatEnComú</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/Catalunya_en_Com%C3%BA_2024_%282%29_Logo.svg/1920px-Catalunya_en_Com%C3%BA_2024_%282%29_Logo.svg.png?utm_source=en.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>#AE355B</t>
   </si>
 </sst>
 </file>
@@ -3473,22 +3464,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C7" s="1">
         <v>3.0</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>32</v>
@@ -3496,19 +3487,19 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1">
         <v>3.0</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>44</v>
@@ -3528,7 +3519,7 @@
         <v>3.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>47</v>
@@ -3551,7 +3542,7 @@
         <v>2.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>52</v>
@@ -3565,22 +3556,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" s="1">
         <v>2.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>17</v>
@@ -3588,19 +3579,19 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1">
         <v>2.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>62</v>
@@ -3620,7 +3611,7 @@
         <v>1.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>64</v>
@@ -3643,7 +3634,7 @@
         <v>1.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>68</v>
@@ -3652,7 +3643,7 @@
         <v>69</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -3666,7 +3657,7 @@
         <v>1.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>72</v>
@@ -3675,7 +3666,7 @@
         <v>73</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H15" s="3"/>
     </row>
@@ -3690,7 +3681,7 @@
         <v>1.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>76</v>
@@ -3713,7 +3704,7 @@
         <v>1.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>80</v>
@@ -3736,7 +3727,7 @@
         <v>1.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>83</v>
@@ -3759,7 +3750,7 @@
         <v>1.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>87</v>
@@ -3882,7 +3873,7 @@
         <v>111</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>32</v>
@@ -3891,10 +3882,10 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C25" s="1">
         <v>1.0</v>
@@ -3903,7 +3894,7 @@
         <v>91</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>118</v>
@@ -4121,7 +4112,7 @@
         <v>156</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35">
@@ -4144,7 +4135,7 @@
         <v>160</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36">
@@ -4279,7 +4270,7 @@
         <v>171</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>187</v>
@@ -4379,7 +4370,7 @@
         <v>202</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46">
@@ -4402,7 +4393,7 @@
         <v>206</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47">
@@ -4632,7 +4623,7 @@
         <v>246</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57">
@@ -4839,7 +4830,7 @@
         <v>284</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66">
@@ -5001,7 +4992,7 @@
         <v>73</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H72" s="6"/>
     </row>
@@ -5022,7 +5013,7 @@
         <v>313</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>32</v>
@@ -5030,10 +5021,10 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C74" s="1">
         <v>1.0</v>
@@ -5042,7 +5033,7 @@
         <v>306</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>73</v>
@@ -5054,10 +5045,10 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C75" s="1">
         <v>1.0</v>
@@ -5066,7 +5057,7 @@
         <v>306</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>73</v>
@@ -5078,10 +5069,10 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="C76" s="1">
         <v>3.0</v>
@@ -5090,10 +5081,10 @@
         <v>306</v>
       </c>
       <c r="E76" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>32</v>
@@ -5101,10 +5092,10 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="C77" s="1">
         <v>2.0</v>
@@ -5113,7 +5104,7 @@
         <v>306</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>331</v>
@@ -5212,7 +5203,7 @@
         <v>344</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="82">
@@ -5465,7 +5456,7 @@
         <v>387</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="93">
@@ -5488,7 +5479,7 @@
         <v>73</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="94">
@@ -5534,7 +5525,7 @@
         <v>398</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="96">
@@ -5603,7 +5594,7 @@
         <v>410</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H98" s="3"/>
     </row>
@@ -5650,7 +5641,7 @@
         <v>418</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101">
@@ -5765,7 +5756,7 @@
         <v>439</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="106">
@@ -5788,7 +5779,7 @@
         <v>73</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="107">
@@ -5811,7 +5802,7 @@
         <v>446</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="108">
@@ -5857,7 +5848,7 @@
         <v>453</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="110">
@@ -5880,7 +5871,7 @@
         <v>457</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111">
@@ -6015,7 +6006,7 @@
         <v>481</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>123</v>
@@ -6023,22 +6014,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="C117" s="1">
         <v>4.0</v>
       </c>
       <c r="D117" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E117" s="2" t="s">
+      <c r="F117" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>32</v>
@@ -6046,22 +6037,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C118" s="1">
         <v>4.0</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>17</v>
@@ -6069,7 +6060,7 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>219</v>
@@ -6078,36 +6069,36 @@
         <v>2.0</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C120" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="C120" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>22</v>
@@ -6115,19 +6106,19 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C121" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C121" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>505</v>
@@ -6147,7 +6138,7 @@
         <v>1.0</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>508</v>
@@ -6156,7 +6147,7 @@
         <v>73</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="123">
@@ -6170,10 +6161,10 @@
         <v>1.0</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>73</v>
@@ -6184,22 +6175,22 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C124" s="1">
         <v>24.0</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>49</v>
@@ -6211,19 +6202,19 @@
         <v>165</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C125" s="1">
         <v>19.0</v>
       </c>
       <c r="D125" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E125" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="F125" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>22</v>
@@ -6231,22 +6222,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C126" s="1">
         <v>1.0</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>32</v>
@@ -6254,22 +6245,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B127" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C127" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="C127" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>22</v>
@@ -6277,7 +6268,7 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>51</v>
@@ -6286,13 +6277,13 @@
         <v>1.0</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E128" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>533</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>32</v>
@@ -6300,25 +6291,25 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="C129" s="1">
         <v>8.0</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>537</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="130">
@@ -6332,7 +6323,7 @@
         <v>8.0</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>540</v>
@@ -6355,7 +6346,7 @@
         <v>7.0</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>544</v>
@@ -6378,7 +6369,7 @@
         <v>1.0</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>548</v>
@@ -6401,7 +6392,7 @@
         <v>4.0</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>552</v>
@@ -6424,7 +6415,7 @@
         <v>2.0</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>556</v>
@@ -6433,7 +6424,7 @@
         <v>557</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="135">
@@ -6447,13 +6438,13 @@
         <v>1.0</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E135" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>17</v>
@@ -6461,22 +6452,22 @@
     </row>
     <row r="136">
       <c r="A136" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C136" s="1">
         <v>2.0</v>
       </c>
       <c r="D136" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>568</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>17</v>
@@ -6485,22 +6476,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C137" s="1">
         <v>2.0</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>49</v>
@@ -6508,7 +6499,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>248</v>
@@ -6517,13 +6508,13 @@
         <v>1.0</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>32</v>
@@ -6531,22 +6522,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C139" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="C139" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>580</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>49</v>
@@ -6554,22 +6545,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="C140" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F140" s="1" t="s">
         <v>581</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>582</v>
-      </c>
-      <c r="C140" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>584</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>27</v>
@@ -6577,22 +6568,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C141" s="1">
         <v>1.0</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E141" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>588</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>22</v>
@@ -6600,22 +6591,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B142" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="C142" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E142" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="C142" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E142" s="2" t="s">
+      <c r="F142" s="1" t="s">
         <v>591</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>12</v>
@@ -6623,22 +6614,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C143" s="1">
         <v>4.0</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>17</v>
@@ -6646,22 +6637,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C144" s="1">
         <v>2.0</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>22</v>
@@ -6669,22 +6660,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C145" s="1">
         <v>1.0</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>49</v>
@@ -6692,22 +6683,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C146" s="1">
         <v>1.0</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>32</v>
@@ -6715,22 +6706,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C147" s="1">
         <v>1.0</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>27</v>
@@ -6738,22 +6729,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B148" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="C148" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="C148" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E148" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>621</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>49</v>
@@ -6761,22 +6752,22 @@
     </row>
     <row r="149">
       <c r="A149" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B149" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="C149" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="C149" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E149" s="2" t="s">
+      <c r="F149" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>625</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>123</v>
@@ -6794,13 +6785,13 @@
         <v>1.0</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>628</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>32</v>
@@ -6809,22 +6800,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B151" s="7" t="s">
         <v>631</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>632</v>
       </c>
       <c r="C151" s="1">
         <v>3.0</v>
       </c>
       <c r="D151" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="F151" s="1" t="s">
         <v>634</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>635</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>17</v>
@@ -6832,22 +6823,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B152" s="7" t="s">
         <v>636</v>
       </c>
-      <c r="B152" s="7" t="s">
+      <c r="C152" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="C152" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E152" s="2" t="s">
+      <c r="F152" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>22</v>
@@ -6858,19 +6849,19 @@
         <v>165</v>
       </c>
       <c r="B153" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C153" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E153" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="C153" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E153" s="2" t="s">
+      <c r="F153" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>32</v>
@@ -6878,22 +6869,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C154" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E154" s="2" t="s">
+      <c r="F154" s="1" t="s">
         <v>645</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>646</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>27</v>
@@ -6901,19 +6892,19 @@
     </row>
     <row r="155">
       <c r="A155" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E155" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="C155" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>650</v>
@@ -6925,7 +6916,7 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>651</v>
@@ -6974,7 +6965,7 @@
         <v>659</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C158" s="1">
         <v>8.0</v>
@@ -7010,7 +7001,7 @@
         <v>665</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>12</v>
@@ -7018,10 +7009,10 @@
     </row>
     <row r="160">
       <c r="A160" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C160" s="1">
         <v>4.0</v>
@@ -7030,10 +7021,10 @@
         <v>660</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>32</v>
@@ -7042,10 +7033,10 @@
     </row>
     <row r="161">
       <c r="A161" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C161" s="1">
         <v>3.0</v>
@@ -7054,10 +7045,10 @@
         <v>660</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>17</v>
@@ -7066,10 +7057,10 @@
     </row>
     <row r="162">
       <c r="A162" s="3" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C162" s="9">
         <v>3.0</v>
@@ -7078,10 +7069,10 @@
         <v>660</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>32</v>
@@ -7090,10 +7081,10 @@
     </row>
     <row r="163">
       <c r="A163" s="3" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="C163" s="1">
         <v>2.0</v>
@@ -7102,10 +7093,10 @@
         <v>660</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>49</v>
@@ -7114,7 +7105,7 @@
     </row>
     <row r="164">
       <c r="A164" s="3" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>404</v>
@@ -7138,10 +7129,10 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="C165" s="1">
         <v>1.0</v>
@@ -7150,21 +7141,21 @@
         <v>660</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="C166" s="1">
         <v>1.0</v>
@@ -7173,10 +7164,10 @@
         <v>660</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>17</v>
@@ -7184,10 +7175,10 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="C167" s="1">
         <v>1.0</v>
@@ -7196,10 +7187,10 @@
         <v>660</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>49</v>
@@ -7207,22 +7198,22 @@
     </row>
     <row r="168">
       <c r="A168" s="3" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="C168" s="1">
         <v>21.0</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>17</v>
@@ -7231,22 +7222,22 @@
     </row>
     <row r="169">
       <c r="A169" s="3" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="C169" s="1">
         <v>20.0</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>49</v>
@@ -7255,22 +7246,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="C170" s="1">
         <v>3.0</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E170" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="F170" s="1" t="s">
         <v>719</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>720</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>49</v>
@@ -7278,7 +7269,7 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>305</v>
@@ -7287,13 +7278,13 @@
         <v>2.0</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E171" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F171" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>723</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>12</v>
@@ -7301,19 +7292,19 @@
     </row>
     <row r="172">
       <c r="A172" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>724</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>725</v>
       </c>
       <c r="C172" s="1">
         <v>2.0</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>727</v>
@@ -7334,37 +7325,37 @@
         <v>1.0</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>730</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H173" s="3"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C174" s="1">
         <v>2.0</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>17</v>
@@ -7373,22 +7364,22 @@
     </row>
     <row r="175">
       <c r="A175" s="3" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C175" s="1">
         <v>3.0</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>22</v>
@@ -7397,19 +7388,19 @@
     </row>
     <row r="176">
       <c r="A176" s="6" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="C176" s="1">
         <v>1.0</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>73</v>
@@ -7421,19 +7412,19 @@
     </row>
     <row r="177">
       <c r="A177" s="6" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="C177" s="1">
         <v>1.0</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>73</v>
@@ -7454,13 +7445,13 @@
         <v>8.0</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>22</v>
@@ -7472,19 +7463,19 @@
         <v>264</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="C179" s="1">
         <v>6.0</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>17</v>
@@ -7493,22 +7484,22 @@
     </row>
     <row r="180">
       <c r="A180" s="3" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="C180" s="1">
         <v>1.0</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>17</v>
@@ -7517,22 +7508,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C181" s="1">
         <v>2.0</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>12</v>
@@ -7540,22 +7531,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C182" s="1">
         <v>2.0</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E182" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>771</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>772</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>32</v>
@@ -7563,25 +7554,25 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="E183" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="C183" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>776</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="184">
@@ -7595,7 +7586,7 @@
         <v>1.0</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>779</v>
@@ -7604,7 +7595,7 @@
         <v>780</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="185">
@@ -7612,7 +7603,7 @@
         <v>264</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="C185" s="1">
         <v>11.0</v>
@@ -7765,7 +7756,7 @@
         <v>806</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="192">
@@ -7812,7 +7803,7 @@
         <v>814</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="194">
@@ -7832,7 +7823,7 @@
         <v>817</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>49</v>
@@ -7840,10 +7831,10 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C195" s="1">
         <v>1.0</v>
@@ -7852,10 +7843,10 @@
         <v>781</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>22</v>
@@ -7863,10 +7854,10 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C196" s="1">
         <v>1.0</v>
@@ -7875,10 +7866,10 @@
         <v>781</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>27</v>
@@ -7886,7 +7877,7 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>297</v>
@@ -7895,13 +7886,13 @@
         <v>6.0</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>32</v>
@@ -7909,45 +7900,45 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="C198" s="1">
         <v>5.0</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="C199" s="1">
         <v>2.0</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>123</v>
@@ -7955,45 +7946,45 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="C200" s="1">
         <v>1.0</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C201" s="1">
         <v>1.0</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>17</v>
@@ -8001,7 +7992,7 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>95</v>
@@ -8010,13 +8001,13 @@
         <v>4.0</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E202" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="F202" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>862</v>
       </c>
       <c r="G202" s="1" t="s">
         <v>17</v>
@@ -8024,19 +8015,19 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>864</v>
       </c>
       <c r="C203" s="1">
         <v>2.0</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>866</v>
@@ -8056,7 +8047,7 @@
         <v>1.0</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>869</v>
@@ -8079,7 +8070,7 @@
         <v>1.0</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>872</v>
@@ -8102,7 +8093,7 @@
         <v>1.0</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>876</v>
@@ -8128,10 +8119,10 @@
         <v>879</v>
       </c>
       <c r="E207" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="F207" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>882</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>17</v>
@@ -8139,10 +8130,10 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>883</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>884</v>
       </c>
       <c r="C208" s="1">
         <v>18.0</v>
@@ -8151,10 +8142,10 @@
         <v>879</v>
       </c>
       <c r="E208" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="F208" s="1" t="s">
         <v>885</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>886</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>22</v>
@@ -8162,10 +8153,10 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>887</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>888</v>
       </c>
       <c r="C209" s="1">
         <v>2.0</v>
@@ -8174,10 +8165,10 @@
         <v>879</v>
       </c>
       <c r="E209" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="F209" s="1" t="s">
         <v>889</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>890</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>22</v>
@@ -8185,10 +8176,10 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C210" s="1">
         <v>6.0</v>
@@ -8197,10 +8188,10 @@
         <v>879</v>
       </c>
       <c r="E210" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="F210" s="1" t="s">
         <v>892</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>893</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>12</v>
@@ -8208,10 +8199,10 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C211" s="1">
         <v>2.0</v>
@@ -8220,13 +8211,13 @@
         <v>879</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>896</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="212">
@@ -8249,7 +8240,7 @@
         <v>900</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="213">
@@ -8269,7 +8260,7 @@
         <v>903</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>27</v>
@@ -8277,10 +8268,10 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C214" s="1">
         <v>1.0</v>
@@ -8289,10 +8280,10 @@
         <v>879</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>123</v>
@@ -8300,10 +8291,10 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C215" s="1">
         <v>1.0</v>
@@ -8312,7 +8303,7 @@
         <v>879</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>73</v>
@@ -8323,10 +8314,10 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="C216" s="1">
         <v>1.0</v>
@@ -8335,7 +8326,7 @@
         <v>879</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>73</v>
@@ -8346,10 +8337,10 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="C217" s="1">
         <v>1.0</v>
@@ -8358,10 +8349,10 @@
         <v>879</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>27</v>
@@ -8369,10 +8360,10 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C218" s="1">
         <v>1.0</v>
@@ -8381,10 +8372,10 @@
         <v>879</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>27</v>
@@ -8392,10 +8383,10 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C219" s="1">
         <v>1.0</v>
@@ -8404,21 +8395,21 @@
         <v>879</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="C220" s="1">
         <v>1.0</v>
@@ -8427,10 +8418,10 @@
         <v>879</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>27</v>
@@ -8438,10 +8429,10 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="C221" s="1">
         <v>1.0</v>
@@ -8450,10 +8441,10 @@
         <v>879</v>
       </c>
       <c r="E221" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="F221" s="1" t="s">
         <v>936</v>
-      </c>
-      <c r="F221" s="1" t="s">
-        <v>937</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>32</v>
@@ -8461,10 +8452,10 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>938</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>939</v>
       </c>
       <c r="C222" s="1">
         <v>1.0</v>
@@ -8473,7 +8464,7 @@
         <v>879</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>941</v>
@@ -8594,7 +8585,7 @@
         <v>959</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="228">
@@ -9042,10 +9033,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1">
         <v>1.0</v>
@@ -9054,33 +9045,33 @@
         <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C8" s="1">
         <v>2.0</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>32</v>
@@ -9088,19 +9079,19 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1">
         <v>4.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>44</v>
@@ -9120,7 +9111,7 @@
         <v>3.0</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>47</v>
@@ -9143,7 +9134,7 @@
         <v>2.0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>52</v>
@@ -9157,22 +9148,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C12" s="1">
         <v>1.0</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>17</v>
@@ -9180,19 +9171,19 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C13" s="1">
         <v>2.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>62</v>
@@ -9212,7 +9203,7 @@
         <v>1.0</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>64</v>
@@ -9235,7 +9226,7 @@
         <v>3.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>68</v>
@@ -9244,7 +9235,7 @@
         <v>69</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -9258,7 +9249,7 @@
         <v>0.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>72</v>
@@ -9267,7 +9258,7 @@
         <v>73</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H16" s="3"/>
     </row>
@@ -9282,7 +9273,7 @@
         <v>1.0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>76</v>
@@ -9305,7 +9296,7 @@
         <v>2.0</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>80</v>
@@ -9328,7 +9319,7 @@
         <v>0.0</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>83</v>
@@ -9351,7 +9342,7 @@
         <v>1.0</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>87</v>
@@ -9380,10 +9371,10 @@
         <v>107</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
@@ -9491,7 +9482,7 @@
         <v>111</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>32</v>
@@ -9500,10 +9491,10 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C27" s="1">
         <v>2.0</v>
@@ -9512,7 +9503,7 @@
         <v>91</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>118</v>
@@ -9691,7 +9682,7 @@
         <v>179</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>49</v>
@@ -9741,7 +9732,7 @@
         <v>156</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
@@ -9761,7 +9752,7 @@
         <v>160</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39">
@@ -9890,7 +9881,7 @@
         <v>171</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>187</v>
@@ -9978,7 +9969,7 @@
         <v>202</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49">
@@ -9998,7 +9989,7 @@
         <v>206</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50">
@@ -10228,7 +10219,7 @@
         <v>246</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60">
@@ -10394,10 +10385,10 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C67" s="1">
         <v>1.0</v>
@@ -10406,10 +10397,10 @@
         <v>261</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>12</v>
@@ -10458,7 +10449,7 @@
         <v>284</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70">
@@ -10614,7 +10605,7 @@
         <v>73</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H76" s="6"/>
     </row>
@@ -10635,7 +10626,7 @@
         <v>313</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>32</v>
@@ -10643,16 +10634,16 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>306</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>73</v>
@@ -10664,16 +10655,16 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>306</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>73</v>
@@ -10685,10 +10676,10 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="C80" s="1">
         <v>4.0</v>
@@ -10697,10 +10688,10 @@
         <v>306</v>
       </c>
       <c r="E80" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>32</v>
@@ -10708,10 +10699,10 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="C81" s="1">
         <v>2.0</v>
@@ -10720,7 +10711,7 @@
         <v>306</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>331</v>
@@ -10816,7 +10807,7 @@
         <v>344</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86">
@@ -11057,7 +11048,7 @@
         <v>387</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="97">
@@ -11077,7 +11068,7 @@
         <v>73</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98">
@@ -11123,7 +11114,7 @@
         <v>398</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100">
@@ -11189,7 +11180,7 @@
         <v>410</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H102" s="3"/>
     </row>
@@ -11233,7 +11224,7 @@
         <v>418</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105">
@@ -11301,7 +11292,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>433</v>
@@ -11324,10 +11315,10 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="C109" s="1">
         <v>4.0</v>
@@ -11342,7 +11333,7 @@
         <v>439</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="110">
@@ -11362,7 +11353,7 @@
         <v>73</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="111">
@@ -11385,7 +11376,7 @@
         <v>446</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="112">
@@ -11428,7 +11419,7 @@
         <v>453</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="114">
@@ -11451,7 +11442,7 @@
         <v>457</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115">
@@ -11479,10 +11470,10 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="C116" s="1">
         <v>2.0</v>
@@ -11491,13 +11482,13 @@
         <v>429</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="117">
@@ -11603,7 +11594,7 @@
         <v>481</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>123</v>
@@ -11611,22 +11602,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="C122" s="1">
         <v>2.0</v>
       </c>
       <c r="D122" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="F122" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>32</v>
@@ -11634,22 +11625,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C123" s="1">
         <v>4.0</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>17</v>
@@ -11657,7 +11648,7 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>219</v>
@@ -11666,33 +11657,33 @@
         <v>3.0</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>501</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>22</v>
@@ -11703,39 +11694,39 @@
         <v>223</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="C126" s="1">
         <v>3.0</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>562</v>
+        <v>586</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>572</v>
+        <v>594</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C127" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C127" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>505</v>
@@ -11752,7 +11743,7 @@
         <v>507</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>508</v>
@@ -11761,7 +11752,7 @@
         <v>73</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="129">
@@ -11772,10 +11763,10 @@
         <v>507</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>73</v>
@@ -11786,45 +11777,45 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>593</v>
+        <v>618</v>
       </c>
       <c r="C130" s="1">
         <v>1.0</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>594</v>
+        <v>620</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C131" s="1">
         <v>23.0</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>49</v>
@@ -11836,19 +11827,19 @@
         <v>165</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C132" s="1">
         <v>19.0</v>
       </c>
       <c r="D132" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="F132" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>22</v>
@@ -11856,19 +11847,19 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>32</v>
@@ -11876,19 +11867,19 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>22</v>
@@ -11896,19 +11887,19 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E135" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>533</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>32</v>
@@ -11916,25 +11907,25 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="C136" s="1">
         <v>12.0</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>537</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="137">
@@ -11948,7 +11939,7 @@
         <v>5.0</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>540</v>
@@ -11962,7 +11953,7 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>543</v>
@@ -11971,7 +11962,7 @@
         <v>5.0</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>544</v>
@@ -11994,7 +11985,7 @@
         <v>6.0</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>548</v>
@@ -12017,7 +12008,7 @@
         <v>3.0</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>552</v>
@@ -12040,7 +12031,7 @@
         <v>2.0</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>556</v>
@@ -12049,7 +12040,7 @@
         <v>557</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="142">
@@ -12063,13 +12054,13 @@
         <v>1.0</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E142" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F142" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>17</v>
@@ -12077,22 +12068,22 @@
     </row>
     <row r="143">
       <c r="A143" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C143" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="E143" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="C143" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D143" s="1" t="s">
+      <c r="F143" s="1" t="s">
         <v>566</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>568</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>17</v>
@@ -12101,22 +12092,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C144" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E144" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="F144" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="C144" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>49</v>
@@ -12124,19 +12115,19 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>248</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>32</v>
@@ -12144,22 +12135,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C146" s="1">
         <v>2.0</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>49</v>
@@ -12167,22 +12158,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C147" s="1">
         <v>2.0</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>27</v>
@@ -12190,19 +12181,19 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E148" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>587</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>588</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>22</v>
@@ -12210,22 +12201,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B149" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="C149" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="C149" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E149" s="2" t="s">
+      <c r="F149" s="1" t="s">
         <v>591</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>595</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>12</v>
@@ -12233,62 +12224,62 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>666</v>
+        <v>692</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>667</v>
+        <v>693</v>
       </c>
       <c r="C150" s="1">
         <v>2.0</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>670</v>
+        <v>696</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>680</v>
+        <v>704</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>681</v>
+        <v>707</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>682</v>
+        <v>708</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>683</v>
+        <v>710</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>691</v>
+        <v>715</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>692</v>
+        <v>716</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>693</v>
+        <v>717</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>702</v>
+        <v>726</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>32</v>
@@ -12296,22 +12287,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C153" s="1">
         <v>3.0</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>17</v>
@@ -12319,22 +12310,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C154" s="1">
         <v>2.0</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>22</v>
@@ -12342,22 +12333,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C155" s="1">
         <v>1.0</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>49</v>
@@ -12365,19 +12356,19 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>32</v>
@@ -12385,22 +12376,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C157" s="1">
         <v>1.0</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>27</v>
@@ -12408,19 +12399,19 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B158" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="F158" s="1" t="s">
         <v>619</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>620</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>621</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>49</v>
@@ -12428,19 +12419,19 @@
     </row>
     <row r="159">
       <c r="A159" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B159" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="B159" s="7" t="s">
+      <c r="D159" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="D159" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="E159" s="2" t="s">
+      <c r="F159" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>625</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>123</v>
@@ -12458,13 +12449,13 @@
         <v>1.0</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>628</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>32</v>
@@ -12473,42 +12464,42 @@
     </row>
     <row r="161">
       <c r="A161" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="s">
-        <v>738</v>
+        <v>758</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C162" s="1">
         <v>2.0</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>739</v>
+        <v>760</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>12</v>
@@ -12516,22 +12507,22 @@
     </row>
     <row r="163">
       <c r="A163" s="6" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>747</v>
+        <v>768</v>
       </c>
       <c r="C163" s="1">
         <v>1.0</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>49</v>
@@ -12539,22 +12530,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B164" s="7" t="s">
         <v>631</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>632</v>
       </c>
       <c r="C164" s="1">
         <v>2.0</v>
       </c>
       <c r="D164" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E164" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="E164" s="2" t="s">
+      <c r="F164" s="1" t="s">
         <v>634</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>635</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>17</v>
@@ -12562,22 +12553,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B165" s="7" t="s">
         <v>636</v>
       </c>
-      <c r="B165" s="7" t="s">
+      <c r="C165" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E165" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="C165" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E165" s="2" t="s">
+      <c r="F165" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>22</v>
@@ -12588,19 +12579,19 @@
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C166" s="1">
         <v>2.0</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E166" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="F166" s="1" t="s">
         <v>641</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>642</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>32</v>
@@ -12608,19 +12599,19 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="D167" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E167" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="D167" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E167" s="2" t="s">
+      <c r="F167" s="1" t="s">
         <v>645</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>646</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>27</v>
@@ -12628,19 +12619,19 @@
     </row>
     <row r="168">
       <c r="A168" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="C168" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E168" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="C168" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>650</v>
@@ -12652,7 +12643,7 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>651</v>
@@ -12701,7 +12692,7 @@
         <v>659</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C171" s="1">
         <v>6.0</v>
@@ -12737,7 +12728,7 @@
         <v>665</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>12</v>
@@ -12745,10 +12736,10 @@
     </row>
     <row r="173">
       <c r="A173" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C173" s="1">
         <v>4.0</v>
@@ -12757,10 +12748,10 @@
         <v>660</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>32</v>
@@ -12769,10 +12760,10 @@
     </row>
     <row r="174">
       <c r="A174" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C174" s="1">
         <v>3.0</v>
@@ -12781,10 +12772,10 @@
         <v>660</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>17</v>
@@ -12793,10 +12784,10 @@
     </row>
     <row r="175">
       <c r="A175" s="3" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C175" s="11">
         <v>5.0</v>
@@ -12805,10 +12796,10 @@
         <v>660</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>32</v>
@@ -12817,19 +12808,19 @@
     </row>
     <row r="176">
       <c r="A176" s="3" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="D176" s="10" t="s">
         <v>660</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>49</v>
@@ -12838,7 +12829,7 @@
     </row>
     <row r="177">
       <c r="A177" s="3" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>404</v>
@@ -12859,39 +12850,39 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="D178" s="10" t="s">
         <v>660</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="D179" s="10" t="s">
         <v>660</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>17</v>
@@ -12899,19 +12890,19 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="D180" s="10" t="s">
         <v>660</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>49</v>
@@ -12919,10 +12910,10 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
-        <v>818</v>
+        <v>834</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>819</v>
+        <v>835</v>
       </c>
       <c r="C181" s="1">
         <v>4.0</v>
@@ -12931,10 +12922,10 @@
         <v>660</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>820</v>
+        <v>838</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>829</v>
+        <v>842</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>49</v>
@@ -12942,10 +12933,10 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>830</v>
+        <v>845</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="C182" s="1">
         <v>3.0</v>
@@ -12954,10 +12945,10 @@
         <v>660</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>832</v>
+        <v>849</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>837</v>
+        <v>855</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>123</v>
@@ -12965,10 +12956,10 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="C183" s="1">
         <v>1.0</v>
@@ -12977,10 +12968,10 @@
         <v>660</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>17</v>
@@ -12988,22 +12979,22 @@
     </row>
     <row r="184">
       <c r="A184" s="3" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="C184" s="1">
         <v>19.0</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>17</v>
@@ -13012,22 +13003,22 @@
     </row>
     <row r="185">
       <c r="A185" s="3" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="C185" s="1">
         <v>13.0</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>49</v>
@@ -13036,22 +13027,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="C186" s="1">
         <v>3.0</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E186" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="F186" s="1" t="s">
         <v>719</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>720</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>49</v>
@@ -13059,7 +13050,7 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>305</v>
@@ -13068,13 +13059,13 @@
         <v>3.0</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E187" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="F187" s="1" t="s">
         <v>722</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>723</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>12</v>
@@ -13082,19 +13073,19 @@
     </row>
     <row r="188">
       <c r="A188" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>724</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>725</v>
       </c>
       <c r="C188" s="1">
         <v>5.0</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>727</v>
@@ -13115,34 +13106,34 @@
         <v>5.0</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>730</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H189" s="3"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="E190" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="F190" s="1" t="s">
         <v>735</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>740</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>17</v>
@@ -13151,22 +13142,22 @@
     </row>
     <row r="191">
       <c r="A191" s="3" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C191" s="1">
         <v>5.0</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>22</v>
@@ -13175,16 +13166,16 @@
     </row>
     <row r="192">
       <c r="A192" s="6" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>73</v>
@@ -13196,16 +13187,16 @@
     </row>
     <row r="193">
       <c r="A193" s="6" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>73</v>
@@ -13226,13 +13217,13 @@
         <v>7.0</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>22</v>
@@ -13244,19 +13235,19 @@
         <v>264</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="C195" s="1">
         <v>6.0</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>17</v>
@@ -13265,19 +13256,19 @@
     </row>
     <row r="196">
       <c r="A196" s="3" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>17</v>
@@ -13286,22 +13277,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="C197" s="1">
         <v>5.0</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="G197" s="1" t="s">
         <v>12</v>
@@ -13309,22 +13300,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C198" s="1">
         <v>2.0</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E198" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="F198" s="1" t="s">
         <v>771</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>772</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>32</v>
@@ -13332,22 +13323,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="D199" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="E199" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>776</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="200">
@@ -13358,7 +13349,7 @@
         <v>778</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>779</v>
@@ -13367,27 +13358,27 @@
         <v>780</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="s">
-        <v>904</v>
+        <v>933</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>905</v>
+        <v>934</v>
       </c>
       <c r="C201" s="1">
         <v>1.0</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>906</v>
+        <v>935</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>916</v>
+        <v>940</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>27</v>
@@ -13398,7 +13389,7 @@
         <v>264</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="C202" s="1">
         <v>7.0</v>
@@ -13542,7 +13533,7 @@
         <v>806</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="209">
@@ -13583,7 +13574,7 @@
         <v>814</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="211">
@@ -13600,7 +13591,7 @@
         <v>817</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>49</v>
@@ -13608,19 +13599,19 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>781</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>22</v>
@@ -13628,19 +13619,19 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>781</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>27</v>
@@ -13648,7 +13639,7 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>297</v>
@@ -13657,13 +13648,13 @@
         <v>4.0</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>32</v>
@@ -13671,45 +13662,45 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="C215" s="1">
         <v>3.0</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="C216" s="1">
         <v>2.0</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>123</v>
@@ -13717,45 +13708,45 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="C217" s="1">
         <v>1.0</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C218" s="1">
         <v>1.0</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>17</v>
@@ -13772,7 +13763,7 @@
         <v>2.0</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E219" s="5" t="s">
         <v>973</v>
@@ -13795,7 +13786,7 @@
         <v>1.0</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>977</v>
@@ -13818,7 +13809,7 @@
         <v>1.0</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E221" s="5" t="s">
         <v>981</v>
@@ -13832,7 +13823,7 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>95</v>
@@ -13841,13 +13832,13 @@
         <v>4.0</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E222" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="F222" s="1" t="s">
         <v>861</v>
-      </c>
-      <c r="F222" s="1" t="s">
-        <v>862</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>17</v>
@@ -13855,19 +13846,19 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>863</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>864</v>
       </c>
       <c r="C223" s="1">
         <v>4.0</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>866</v>
@@ -13884,7 +13875,7 @@
         <v>868</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>869</v>
@@ -13907,7 +13898,7 @@
         <v>1.0</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>872</v>
@@ -13927,7 +13918,7 @@
         <v>875</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>876</v>
@@ -13947,7 +13938,7 @@
         <v>983</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E227" s="5" t="s">
         <v>984</v>
@@ -13956,7 +13947,7 @@
         <v>985</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="228">
@@ -13973,10 +13964,10 @@
         <v>879</v>
       </c>
       <c r="E228" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="F228" s="1" t="s">
         <v>881</v>
-      </c>
-      <c r="F228" s="1" t="s">
-        <v>882</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>17</v>
@@ -13984,10 +13975,10 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>883</v>
-      </c>
-      <c r="B229" s="1" t="s">
-        <v>884</v>
       </c>
       <c r="C229" s="1">
         <v>17.0</v>
@@ -13996,10 +13987,10 @@
         <v>879</v>
       </c>
       <c r="E229" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="F229" s="1" t="s">
         <v>885</v>
-      </c>
-      <c r="F229" s="1" t="s">
-        <v>886</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>22</v>
@@ -14007,10 +13998,10 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>887</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>888</v>
       </c>
       <c r="C230" s="1">
         <v>1.0</v>
@@ -14019,10 +14010,10 @@
         <v>879</v>
       </c>
       <c r="E230" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="F230" s="1" t="s">
         <v>889</v>
-      </c>
-      <c r="F230" s="1" t="s">
-        <v>890</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>22</v>
@@ -14030,10 +14021,10 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C231" s="1">
         <v>12.0</v>
@@ -14042,10 +14033,10 @@
         <v>879</v>
       </c>
       <c r="E231" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="F231" s="1" t="s">
         <v>892</v>
-      </c>
-      <c r="F231" s="1" t="s">
-        <v>893</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>12</v>
@@ -14053,10 +14044,10 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C232" s="1">
         <v>2.0</v>
@@ -14065,13 +14056,13 @@
         <v>879</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>896</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="233">
@@ -14094,12 +14085,12 @@
         <v>900</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="s">
-        <v>901</v>
+        <v>986</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>902</v>
@@ -14114,7 +14105,7 @@
         <v>903</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>27</v>
@@ -14122,10 +14113,10 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C235" s="1">
         <v>1.0</v>
@@ -14134,10 +14125,10 @@
         <v>879</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>123</v>
@@ -14145,16 +14136,16 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>879</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>73</v>
@@ -14165,16 +14156,16 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>879</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>73</v>
@@ -14185,10 +14176,10 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="C238" s="1">
         <v>1.0</v>
@@ -14197,10 +14188,10 @@
         <v>879</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>27</v>
@@ -14208,10 +14199,10 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C239" s="1">
         <v>1.0</v>
@@ -14220,10 +14211,10 @@
         <v>879</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>27</v>
@@ -14231,25 +14222,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="s">
-        <v>986</v>
+        <v>922</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="C240" s="1">
-        <v>1.0</v>
+        <v>923</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>879</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>988</v>
+        <v>924</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>989</v>
+        <v>925</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="241">
@@ -14269,7 +14257,7 @@
         <v>929</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
     </row>
     <row r="242">
@@ -14286,27 +14274,27 @@
         <v>932</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>879</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>32</v>
@@ -14314,145 +14302,148 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>939</v>
+        <v>943</v>
+      </c>
+      <c r="C244" s="1">
+        <v>7.0</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>879</v>
+        <v>944</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>943</v>
+        <v>256</v>
       </c>
       <c r="C245" s="1">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>944</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>256</v>
+        <v>951</v>
       </c>
       <c r="C246" s="1">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>944</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>951</v>
+        <v>871</v>
       </c>
       <c r="C247" s="1">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>944</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>871</v>
+        <v>228</v>
       </c>
       <c r="C248" s="1">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>944</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="s">
-        <v>957</v>
+        <v>288</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>228</v>
+        <v>960</v>
       </c>
       <c r="C249" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>944</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="s">
-        <v>288</v>
+        <v>963</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C250" s="1">
         <v>1.0</v>
@@ -14461,55 +14452,32 @@
         <v>944</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="C251" s="1">
-        <v>1.0</v>
+        <v>968</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>944</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>968</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="F252" s="1" t="s">
-        <v>970</v>
-      </c>
-      <c r="G252" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -14752,8 +14720,7 @@
     <hyperlink r:id="rId235" ref="E249"/>
     <hyperlink r:id="rId236" ref="E250"/>
     <hyperlink r:id="rId237" ref="E251"/>
-    <hyperlink r:id="rId238" ref="E252"/>
   </hyperlinks>
-  <drawing r:id="rId239"/>
+  <drawing r:id="rId238"/>
 </worksheet>
 </file>